--- a/llm/evaluation/annotation/calibration/annotator2.xlsx
+++ b/llm/evaluation/annotation/calibration/annotator2.xlsx
@@ -428,17 +428,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,20 +471,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>annotator_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>abstain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hallucinated</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>wrong_claims</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>faithfulness_level</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>approach_match</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>domain_familiarity</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -555,10 +597,21 @@
 With this approach, you should see each field instance correctly receive its respective class based on its content, such as `rating-1`, `rating-5`, and `rating-8`, without the overlap you were experiencing previously.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -764,7 +817,7 @@
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>To address the issue of EditText fields snapping into view on smaller mobile displays, you can use a `ScrollView` to allow the entire form to be scrollable. This setup should enable the view to adjust when the keyboard appears, making sure that all fields including the 'Next' button are visible.
-Here’s an example implementation based on the context provided:
+Here’s an example implementation:
 1. **Wrap your layout in a ScrollView**: The top-level layout in your XML should be a `ScrollView`. This will allow the user to scroll through the form when the keyboard is visible.
  ```xml
  &lt;ScrollView
@@ -775,12 +828,12 @@
  &lt;RelativeLayout
  android:layout_width="match_parent"
  android:layout_height="wrap_content"&gt;
- ...
+...
  &lt;/RelativeLayout&gt;
  &lt;/ScrollView&gt;
  ```
- The `fillViewport` attribute can be set to true to ensure that the ScrollView fills the available space, which can improve the layout’s behavior when the keyboard is presented .
-2. **Use appropriate layout parameters**: Make sure your child layouts (like `RelativeLayout` for your login fields) are set properly to `wrap_content` for height so that they don't take unnecessary space when the keyboard is up .
+ The `fillViewport` attribute can be set to true to ensure that the ScrollView fills the available space, which can improve the layout’s behavior when the keyboard is presented.
+2. **Use appropriate layout parameters**: Make sure your child layouts (like `RelativeLayout` for your login fields) are set properly to `wrap_content` for height so that they don't take unnecessary space when the keyboard is up.
 3. **Consider using ViewTreeObserver.OnGlobalLayoutListener**: By implementing `ViewTreeObserver.OnGlobalLayoutListener`, you can detect when the keyboard is open and potentially scroll the view to ensure that the relevant EditText fields and buttons are always visible when focused. Here’s a snippet:
  ```java
  scrollView.getViewTreeObserver().addOnGlobalLayoutListener(new ViewTreeObserver.OnGlobalLayoutListener() {
@@ -790,14 +843,215 @@
  }
  });
  ```
- This strategy was mentioned in the context .
+ This strategy was mentioned.
 By implementing these strategies, you should achieve an improved user experience where all form fields and buttons are visible when interacting with the EditText fields, especially on smaller screens.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+gt;
+            &amp;lt;TextView
+                android:id="@+id/anyid"
+                android:layout_width="wrap_content"
+                android:layout_height="wrap_content"
+                android:layout_gravity="center"/&amp;gt;
+            &amp;lt;Button
+                android:layout_width="wrap_content"
+                android:layout_height="55dp"
+                android:id="@+id/anyotherid"
+                style="@style/AppTheme.Button"
+                android:layout_marginTop="20dp"
+                android:layout_gravity="center_horizontal"
+                android:textStyle="bold"
+                android:padding="10dp"
+                android:textSize="20sp"
+                android:text="Submit"/&amp;gt;
+        &amp;lt;/LinearLayout&amp;gt;
+    &amp;lt;/ScrollView&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;This works great for me. :)&lt;/p&gt;
+[K2]
+ android:inputType="textPassword"
+    android:ems="10"
+    android:id="@+id/loginPassword_id"
+    android:textAlignment="center"
+    android:hint="Enter Application Password"
+    android:textColor="#ffffff"
+    android:textColorHint="#000000"
+    android:layout_below="@+id/appLogoImage_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+    android:layout_alignParentEnd="true"
+    android:layout_marginTop="@dimen/margin_50"
+    android:background="@android:color/transparent"
+    android:visibility="visible"
+    android:textCursorDrawable="@drawable/white_cursor" /&amp;gt;
+&amp;lt;TextView
+    android:layout_width="wrap_content"
+    android:layout_height="wrap_content"
+    android:textAppearance="?android:attr/textAppearanceMedium"
+    android:text="REGISTRATION"
+    android:id="@+id/regTitle_id"
+    android:layout_below="@+id/appLogoImage_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+    android:layout_alignParentEnd="true"
+    android:textColor="#ffffff"
+    android:textAlignment="center"
+    android:layout_marginTop="@dimen/margin_50"
+    android:visibility="invisible"
+    android:textStyle="bold" /&amp;gt;
+&amp;lt;EditText
+    android:layout_width="wrap_content"
+    android:layout_height="wrap_content"
+    android:inputType="textNoSuggestions|text"
+    android:ems="10"
+    android:id="@+id/regName_id"
+    android:layout_below="@+id/loginPassword_id"
+    android:layout_alignParentLeft="true"
+    android:layout_alignParentStart="true"
+    android:layout_alignParentRight="true"
+[K3]
+ android:layout_centerHorizontal="true"
+        android:layout_marginTop="96dp"
+        android:id="@+id/editText3"
+        android:hint="password" /&amp;gt;
+    &amp;lt;EditText
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:inputType="textPassword"
+        android:ems="10"
+        android:layout_below="@+id/editText3"
+        android:layout_alignRight="@+id/editText3"
+        android:layout_alignEnd="@+id/editText3"
+        android:id="@+id/editText4"
+        android:hint="confirm" /&amp;gt;
+    &amp;lt;Button
+        android:text="SIGN IN"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:layout_alignParentBottom="true"
+        android:id="@+id/button2"
+        android:layout_below="@+id/editText4"
+        android:layout_centerHorizontal="true" /&amp;gt;
+&amp;lt;/RelativeLayout&amp;gt;
+    &amp;lt;/ScrollView&amp;gt;
+&amp;lt;/RelativeLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;In your &lt;code&gt;Activity&lt;/code&gt; set the referance of the &lt;code&gt;ScrollView&lt;/code&gt; and the main &lt;code&gt;RelativeLayout&lt;/code&gt;
+Also set &lt;code&gt;ViewTreeObserver.OnGlobalLayoutListener&lt;/code&gt; on your main &lt;code&gt;RelativeLayout&lt;/code&gt; and implements the &lt;code&gt;onGlobalLayout()&lt;/code&gt; method.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Take a look at the example below:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;public class MainActivity extends AppCompatActivity implements ViewTreeObserver.OnGlobalLayoutListener {
+    private ScrollView scrollView;
+    private RelativeLayout activity_main_RL;
+    @Override
+    protected void onCreate(Bundle savedInstanceState) {
+        super.onCreate(savedInstanceState);
+        setContentView(R.layout.activity_main);
+        scrollView = (ScrollView) findViewById(R.id.scroolView);
+        activity_main_RL =
+[K4]
+Q: Android - Struggiling to layout my application when virtual keyboard is visible
+A: &lt;p&gt;What I usually do is using &lt;code&gt;ScrollView&lt;/code&gt;:&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://i.sstatic.net/lERk2.gif" rel="nofollow noreferrer"&gt;&lt;img src="https://i.sstatic.net/lERk2.gif" alt="enter image description here"&gt;&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Define the &lt;code&gt;ScroolView&lt;/code&gt; in your &lt;code&gt;Layout&lt;/code&gt; like below (or just copy paste the code):&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;RelativeLayout
+    xmlns:android="http://schemas.android.com/apk/res/android"
+    xmlns:tools="http://schemas.android.com/tools"
+    android:id="@+id/activity_main"
+    android:layout_width="match_parent"
+    android:layout_height="match_parent"
+    tools:context="com.igor.test.MainActivity"&amp;gt;
+    &amp;lt;android.support.v7.widget.Toolbar
+        android:layout_width="match_parent"
+        android:layout_height="wrap_content"
+        android:background="?attr/colorPrimary"
+        android:theme="?attr/actionBarTheme"
+        android:minHeight="?attr/actionBarSize"
+        android:layout_alignParentTop="true"
+        android:layout_alignParentLeft="true"
+        android:layout_alignParentStart="true"
+        android:id="@+id/appTitleBar"
+        android:elevation="4dp"&amp;gt;
+        &amp;lt;TextView
+            android:text="@string/app_name"
+            android:layout_width="wrap_content"
+            android:layout_height="wrap_content"
+            android:id="@+id/toolbarText"
+            android:textAppearance="@style/TextAppearance.AppCompat.Title"
+            android:textColor="?android:attr/textColorPrimaryInverse" /&amp;gt;
+    &amp;lt;/android.support.v7.widget.Toolbar&amp;gt;
+    &amp;lt;android.support.v7
+[K5]
+    android:layout_marginTop="20dp"
+    android:gravity="center_horizontal"
+    android:orientation="horizontal"&amp;gt;
+    &amp;lt;TextView
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:drawableLeft="@drawable/msg" /&amp;gt;
+    &amp;lt;EditText
+        android:id="@+id/e1"
+        android:layout_width="300dp"
+        android:layout_height="wrap_content"
+        android:hint="  E-Mail/Adresse" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&amp;lt;LinearLayout
+    android:layout_width="match_parent"
+    android:layout_height="wrap_content"
+    android:gravity="center_horizontal"
+    android:orientation="horizontal"&amp;gt;
+    &amp;lt;TextView
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:drawableLeft="@drawable/lock" /&amp;gt;
+    &amp;lt;EditText
+        android:id="@+id/e2"
+        android:layout_width="300dp"
+        android:layout_height="wrap_content"
+        android:hint="  Password"
+        android:paddingTop="12dp" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&amp;lt;LinearLayout
+    android:layout_width="match_parent"
+    android:layout_height="match_parent"
+    android:gravity="center"&amp;gt;
+    &amp;lt;Button
+        android:id="@+id/b1"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:text="Sign In" /&amp;gt;
+    &amp;lt;Button
+        android:id="@+id/b2"
+        android:layout_width="wrap_content"
+        android:layout_height="wrap_content"
+        android:text="Register" /&amp;gt;
+&amp;lt;/LinearLayout&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;the src for the imageview bg.xml is &lt;/p&gt;
+&lt;pre</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -929,10 +1183,21 @@
 By following the above steps, you should be able to resolve the dependency issues and successfully build your project. If problems persist, please provide any additional error messages or logs that may help in diagnosing the problem further.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -963,13 +1228,126 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific details regarding the support of JDK 11 in AWS Lambda or the use of Corretto 11 with AWS Lambda. Therefore, I cannot provide a definitive answer to the question about AWS Lambda's support for JDK 11. If you need information on how to resolve deployment issues or further details regarding Java version compatibility in AWS Lambda, the context also does not provide any information related to that.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific details regarding the support of JDK 11 in AWS Lambda or the use of Corretto 11 with AWS Lambda. Therefore, I cannot provide a definitive answer to the question about AWS Lambda's support for JDK 11. If you need information on how to resolve deployment issues or further details regarding Java version compatibility in AWS Lambda, the context also does not provide any information related to that.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+$registerAndPromoteBean$1(AwsSecretsManagerConfigDataLocationResolver.java:113) ~[spring-cloud-starter-aws-secrets-manager-config-2.3.0-RC2.jar:2.3.0-RC2]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.doInvokeListener(SimpleApplicationEventMulticaster.java:176) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.invokeListener(SimpleApplicationEventMulticaster.java:169) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:143) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:131) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.boot.DefaultBootstrapContext.close(DefaultBootstrapContext.java:133) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.prepareContext(SpringApplication.java:392) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:325) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1311) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1300) ~[spring-boot-2.4.2.jar:2.4.2]
+        at com.brighttalk.service.securedsecrets
+[K2]
+Q: Tomcat fails to start using Eclipse, JRebel, and Spring Boot
+A: &lt;p&gt;JRebel cannot instrument class because &lt;em&gt;MBeanRegistrationSupport#setRegistrationBehavior&lt;/em&gt; method was removed by &lt;a href="https://github.com/spring-projects/spring-framework/commit/b5db5d3aac39ca7cff4ccca491652d9490a1d175#diff-c36e12d89e096da6108d667fb27b1c3dL165" rel="nofollow"&gt;b5db5d&lt;/a&gt; commit on spring-framework development branch.&lt;/p&gt;
+&lt;p&gt;We have updated our Spring integration and &lt;a href="https://zeroturnaround.com/software/jrebel/download/nightly-build/" rel="nofollow"&gt;JRebel Nighly build&lt;/a&gt; (choose standalone jar) should work fine.&lt;/p&gt;
+&lt;p&gt;Fix will be included in JRebel 6.5.2 which we plan to release next week.&lt;/p&gt;
+&lt;p&gt;Thank you for bug report, if you have any questions/issue please write to support@zeroturnaround.com.&lt;/p&gt;
+[K3]
+Q: SpringMVC XML error- Randomly
+A: &lt;p&gt;This kind of issue:&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;cvc-elt.1: Cannot find the declaration of element 'beans'.
+  root-context.xml /SwiftEmploymentMVC/src/main/webapp/WEB-INF/spring
+  line 3 XML Problem&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;generally is a &lt;strong&gt;dependency one&lt;/strong&gt;, that is caused by some &lt;strong&gt;missing classes&lt;/strong&gt;, themselves caused by using &lt;strong&gt;conflicting dependencies versions&lt;/strong&gt;.
+Even if you say everything is fine with your Apache server, you are using &lt;strong&gt;too much different versions for your Spring jars&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;By example, you use &lt;code&gt;spring-security-core&lt;/code&gt; in version &lt;code&gt;3.1.0.RELEASE&lt;/code&gt;, but &lt;code&gt;spring-security-config&lt;/code&gt; in version &lt;code&gt;4.0.3.RELEASE&lt;/code&gt;.
+Those jars are linked, and you are using 2 different major versions, which could be a problem.&lt;/p&gt;
+&lt;p&gt;If you don't know &lt;strong&gt;which dependencies versions are required by a jar&lt;/strong&gt;, have a look at &lt;a href="http://mvnrepository.com/" rel="nofollow"&gt;http://mvnrepository.com/&lt;/a&gt;.&lt;br&gt;
+It lists the different required dependencies by type.&lt;/p&gt;
+&lt;p&gt;If your case, I would suggest that you use your &lt;code&gt;org.springframework-version&lt;/code&gt; property for more (or all) of your Spring jars.&lt;/p&gt;
+[K4]
+Q: Error Creating Bean Error (Spring Cloud Config Client)
+A: &lt;p&gt;With help for Gregor, I was able to solve it. These are the changes I did:&lt;/p&gt;
+&lt;p&gt;I added a &lt;code&gt;messageConverter&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package com.gcp.logicalprovisioning.config.server;
+import org.slf4j.Logger;
+import org.slf4j.LoggerFactory;
+import org.springframework.beans.factory.annotation.Value;
+import org.springframework.boot.CommandLineRunner;
+import org.springframework.boot.SpringApplication;
+import org.springframework.boot.autoconfigure.EnableAutoConfiguration;
+import org.springframework.boot.autoconfigure.SpringBootApplication;
+import org.springframework.boot.autoconfigure.jdbc.DataSourceAutoConfiguration;
+import org.springframework.context.annotation.Bean;
+@SpringBootApplication
+@EnableAutoConfiguration(exclude={DataSourceAutoConfiguration.class})
+public class DemoClientApplication {
+    private static final Logger LOGGER = LoggerFactory.getLogger(DemoClientApplication.class);
+    public static void main(String[] args) {
+        SpringApplication.run(DemoClientApplication.class, args);
+    }
+    /**
+     * Output property from cloud-config-server on startup of app,
+     *
+     * also can be seen at:
+     * http://localhost:9090/env/APP.aaf.env
+     */
+    @Bean
+    public CommandLineRunner printProperties(@Value(&amp;quot;${APP.aaf.env}&amp;quot;) final String appProperty)  {
+        return args -&amp;gt; LOGGER.info(&amp;quot;APP.aaf.env is: [{}]&amp;quot;, appProperty);
+    }
+    @Bean
+    public RestTemplate restTemplate() {
+        final RestTemplate restTemplate = new RestTemplate();
+        List&amp;lt;HttpMessageConverter&amp;lt;?&amp;gt;&amp;gt; messageConverters = new ArrayList&amp;lt;&amp;gt;();
+        MappingJackson2HttpMessageConverter mappingJackson2HttpMessageConverter = new MappingJackson2HttpMessageConverter();
+        mappingJackson2HttpMessageConverter.setSupportedMediaTypes(Collections.singletonList(MediaType.ALL));
+        messageConverters.add(mappingJackson2HttpMessageConverter);
+        restTemplate.setMessageConverters(messageConverters
+[K5]
+Q: spring batch AsynchJob Launcher ,Error in setting job repo
+A: &lt;p&gt;Here is a working example made from &lt;a href="http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/" rel="nofollow"&gt;http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/&lt;/a&gt; and tested on wildfly 9.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;beans xmlns="http://www.springframework.org/schema/beans"
+       xmlns:batch="http://www.springframework.org/schema/batch" 
+       xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"
+       xsi:schemaLocation="http://www.springframework.org/schema/batch
+        http://www.springframework.org/schema/batch/spring-batch-2.2.xsd
+        http://www.springframework.org/schema/beans 
+        http://www.springframework.org/schema/beans/spring-beans-3.2.xsd
+    "&amp;gt;
+    &amp;lt;bean id="report" class="Report" scope="prototype" /&amp;gt;
+    &amp;lt;bean id="jobRepository"
+       class="org.springframework.batch.core.repository.support.MapJobRepositoryFactoryBean"&amp;gt;
+        &amp;lt;property name="transactionManager" ref="transactionManager" /&amp;gt;
+    &amp;lt;/bean&amp;gt;
+    &amp;lt;batch:job id="helloWorldJob"&amp;gt;
+        &amp;lt;batch:step id="step1"&amp;gt;
+            &amp;lt;batch:tasklet&amp;gt;
+                &amp;lt;batch:chunk reader="cvsItemReader" writer="xmlItemWriter"
+                                     commit-interval="10"&amp;gt;
+                &amp;lt;/batch:chunk&amp;gt;
+            &amp;lt;/batch:tasklet&amp;gt;
+        &amp;lt;/batch:step&amp;gt;
+    &amp;lt;/batch:job&amp;gt;
+    &amp;lt;bean id="jobLauncher"
+              class="org</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -997,13 +1375,58 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the issue of a Blackberry application description text error for more than 255 characters. No information is provided regarding the specific error mentioned in the context.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the issue of a Blackberry application description text error for more than 255 characters. No information is provided regarding the specific error mentioned.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Blackberry @Override notation error
+A: &lt;p&gt;Blackberry development is built on top of j2me, which has the language features of Java 1.3.  This means it doesn't support annotations. You can remove the @Override annotations and your code will work.  Remember these are optional although recommended anyways.&lt;/p&gt;
+&lt;p&gt;What I do, is write //@Override instead. When/If annotations are added in the future it will be easy to do a regex replace and remove the comment marks.&lt;/p&gt;
+[K2]
+Q: java.io.UnsupportedEncodingException: ISO-8859-8, text/xml
+A: &lt;p&gt;&lt;code&gt;ISO-8859-8&lt;/code&gt; is not one of the &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/StandardCharsets.html" rel="nofollow noreferrer"&gt;standard charsets&lt;/a&gt; that Java &lt;em&gt;needs&lt;/em&gt; to support, i.e. which are guaranteed to be found (unless you have a corrupted installation).&lt;/p&gt;
+&lt;p&gt;In your case, the difference seems to be in the Windows 10 environment. I would check first that it has support for &lt;code&gt;ISO-8859-8&lt;/code&gt; (I don't know how though, I'm not a Windows user). It may need to be installed/enabled separately.&lt;/p&gt;
+&lt;p&gt;If you're &lt;strong&gt;certain&lt;/strong&gt; that your Windows 10 does support that encoding, then it's a problem with Java not being able to make the connection between the two, and you'll probably have to delve into &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/spi/CharsetProvider.html" rel="nofollow noreferrer"&gt;charset providers&lt;/a&gt;, but let's hope you don't have to go there.&lt;/p&gt;
+[K3]
+Q: The encoding 'UTF-8' is not supported by the Java runtime
+A: &lt;p&gt;Most probably someone put a catch() expecting to have only unsupported encoding exceptions, so he used the appropriate message. But he has used too wide exception specification (e.g. catch( Exception ex ) ), so when at runtime he's got something else (non-valid XML, NPE, ... ) the message became misleading.&lt;/p&gt;
+[K4]
+Q: Does Blackberry support Android OS
+A: &lt;p&gt;Although Android and Blackberry both use Java, they expose very different application APIs to developers.  So I don't think it is possible to run Android apps on a Blackberry - YET.  RIM has already announced that they are planning on supporting Android apps on the upcoming Blackberry Playbook tablet.&lt;/p&gt;
+[K5]
+Q: Eclipse - "Incompatible JVM. Version 1.8.0_261 of the JVM is not suitable for this product. Version: 11 or greater is required"
+A: &lt;p&gt;For Ubuntu users, refer to the answer &lt;a href="https://stackoverflow.com/a/64049648/14489697"&gt;https://stackoverflow.com/a/64049648/14489697&lt;/a&gt; by howlger. Add the following lines in file &lt;code&gt;eclipse.ini&lt;/code&gt; before &lt;code&gt;-vmargs&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-none prettyprint-override"&gt;&lt;code&gt;-vm
+/usr/lib/jvm/adoptopenjdk-14-openj9-amd64/bin/java
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Above is the Java install location. Change this according to yours.&lt;/p&gt;
+&lt;p&gt;I'm using,&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Eclipse IDE for Enterprise Java Developers (includes Incubating components)&lt;/li&gt;
+&lt;li&gt;Version: 2020-12 (4.18.0)&lt;/li&gt;
+&lt;li&gt;Build id: 20201210-1552&lt;/li&gt;
+&lt;li&gt;OS: Linux, v.5.4.0-42-generic, x86_64 / gtk 3.22.30&lt;/li&gt;
+&lt;li&gt;Java version: 14.0.2&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1067,10 +1490,82 @@
 These steps generally help resolve issues related to pushing changes to a remote repository when faced with errors about missing objects or invalid references.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: remote: fatal: fsck error in packed object when pushing oh-my-zsh repo to new remote
+A: &lt;p&gt;&lt;a href="https://gitlab.com/gitlab-org/gitaly/issues/787" rel="nofollow noreferrer"&gt;In theory, this was already fixed at GitLab.&lt;/a&gt;  Why it is showing up for you, I have no idea.&lt;/p&gt;
+&lt;p&gt;The problem here is that &lt;code&gt;https://github.com/robbyrussell/oh-my-zsh&lt;/code&gt; itself is (somewhat) broken.  This has nothing to do with anything you did.  Meanwhile, your &lt;code&gt;gitlab.com&lt;/code&gt; service is configured to be ultra-strict.  This &lt;em&gt;also&lt;/em&gt; &lt;strong&gt;probably&lt;/strong&gt; has nothing to do with anything you did—but you'll need to change it, or else give up on the idea of sending &lt;em&gt;this&lt;/em&gt; repository to &lt;code&gt;gitlab.com&lt;/code&gt;.  (Or, perhaps your best bet, get them to note that their fix has un-fixed itself.)&lt;/p&gt;
+&lt;p&gt;If you clone the URL above and run &lt;code&gt;git fsck&lt;/code&gt; on your own clone, you'll see this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ git fsck
+Checking object directories: 100% (256/256), done.
+warning in tree 2b7227859263b6aabcc28355b0b994995b7148b6: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree a18c4d13c2a5fa2d4ecd5346c50e119b999b807d: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree 84df066176c8da3fd59b13731a86d90f4f1e5c9d: zeroPaddedFile
+[K2]
+Q: GIT 2nd PUSH is failing
+A: &lt;blockquote&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Git will not allow you to push changes if our branch is not up to date with the server&lt;/p&gt;
+&lt;p&gt;Once you try to &lt;code&gt;push&lt;/code&gt; your code to the remote repo git verify that your &amp;quot;local&amp;quot; branch has all the latest code from the remote branch. If it see that you are missing some commits it will not let you push the code to the remote.&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h3&gt;How to fix it?&lt;/h3&gt;
+&lt;p&gt;Its very simple - you simply need to pull the changes from the server in one of the following ways:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;# assuming you are on the desired branch
+# update your local server with all the latest code from the server
+# This is an optional command but its a good practice to always be 
+# synchronized with the server
+git fetch --all --prune
+# now pull (pull = fetch + merge) the changes from the server to your branch
+git pull origin &amp;lt;branch name&amp;gt;
+# now your local branch is up to date and contains all the &amp;quot;server&amp;quot; code as well
+# push your changes to the remote branch
+git push origin &amp;lt;branch name&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: "fatal: strange pathname '-im/somerepo.git' blocked
+A: &lt;p&gt;The leading &lt;code&gt;-&lt;/code&gt; character caused security issues in previous versions of git. It seems your Ubuntu installation contains the fixed Debian version that blocks your fetch attempt. You should rename the repository on BitBucket, and update your local configuration accordingly.&lt;/p&gt;
+&lt;p&gt;&lt;a href="http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2" rel="nofollow noreferrer"&gt;http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff" rel="nofollow noreferrer"&gt;https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: GitHub repository disabled when changing from private to public
+A: &lt;p&gt;Contacted GitHub support and they unlocked the repository. It may have happened because I changed the repo from private to public during their outage. Everything works fine now&lt;/p&gt;
+[K5]
+Q: merging local repo with github repo is resulting in a fatal error
+A: &lt;p&gt;Errors tell that your local branch is behind from master.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;1) Try &lt;code&gt;git pull origin master --rebase&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;if it does not work then local and remote branch, not in sync.
+you have to first sync your local master branch with remote master.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;follow following steps:&lt;/strong&gt;&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;copy your new commit hash which you recently commit.&lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git fetch origin&lt;/code&gt; &lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git reset --hard origin/master&lt;/code&gt; # to sync your
+local master with remoter master &lt;/li&gt;
+&lt;li&gt;cherry-pick your commit: &lt;code&gt;git cherry-pick your_commit_hash&lt;/code&gt;&lt;/li&gt;
+&lt;li&gt;&lt;code&gt;git push origin master&lt;/code&gt; # to push your commit
+Let me know if it still not resolved.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Thanks!&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1124,10 +1619,21 @@
 Integrating a fully-fledged WYSIWYG HTML editor in a Windows Mobile app is challenging due to platform limitations. Consider the above suggestions and determine what aligns best with your requirements and user needs. If developing from scratch, start simple, and you can always iterate and add features based on user feedback.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1234,10 +1740,125 @@
 By following these guidance points, you should be able to resolve the errors related to your Firebase and Android Support library dependencies effectively.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: "com.android.support:appcompat-v7:28.0.0" Error
+A: &lt;pre&gt;&lt;code&gt;implementation 'com.android.support:support-media-compat:28.0.0'
+implementation 'com.android.support:support-v4:28.0.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;add to dependencies and change &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:16.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;to &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;implementation 'com.google.firebase:firebase-database:9.0.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;This is working for me&lt;/p&gt;
+[K2]
+0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CONFIG_VERSION&amp;quot;: &amp;quot;21.2.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_VERSION&amp;quot;: &amp;quot;20.3.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_AUTH_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FIRESTORE_VERSION&amp;quot;: &amp;quot;24.4.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_FUNCTIONS_VERSION&amp;quot;: &amp;quot;20.2.1&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_IID_VERSION&amp;quot;: &amp;quot;21.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_INSTALLATIONS_VERSION&amp;quot;: &amp;quot;17.1.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_CRASHLYTICS_NDK_VERSION&amp;quot;: &amp;quot;18.3.2&amp;quot;,
+        &amp;quot;ANDROID_GSON_VERSION&amp;quot;: &amp;quot;2.9.0&amp;quot;,
+        &amp;quot;ANDROID_FIREBASE_PERF_GRADLE_PLUGIN_VERSION&amp;quot;: &amp;quot;1.4.2&amp;quot;,
+        &amp;quot;ANDROID_GRPC_OKHTTP&amp;quot;: &amp;quot;1.46.0&amp;quot;,
+        &amp;quot;IOS_USE_PRECOMPILED_FIRESTORE_POD&amp;quot;: &amp;quot;false&amp;quot;
+      },
+      &amp;quot;cordova-plugin-androidx-adapter&amp;quot;: {}
+    },
+    &amp;quot;platforms&amp;quot;: [
+      &amp;quot;browser&amp;quot;,
+      &amp;quot;ios&amp;quot;,
+      &amp;quot;android&amp;quot;
+    ]
+  }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;References:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;a href="https://developer.apple.com
+[K3]
+Q: I keep receiving a gradle sync error when trying to add Firebase UI 2.3.0
+A: &lt;p&gt;Since you are using &lt;code&gt;com.android.support:customtabs:26.0.1&lt;/code&gt; you have to add in the &lt;code&gt;repositories&lt;/code&gt; the "&lt;a href="https://maven.google.com" rel="nofollow noreferrer"&gt;https://maven.google.com&lt;/a&gt;" endpoint.&lt;br&gt;
+All the support libraries since 25.4.0 are in the google maven repo as &lt;a href="https://developer.android.com/topic/libraries/support-library/revisions.html#25-4-0" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;In your case something like;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;allprojects {
+    repositories {
+        jcenter()
+        maven { url 'https://maven.fabric.io/public' }  // &amp;lt;= ADD THIS
+        maven {
+            url "https://maven.google.com"
+        }
+    }
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Also if you want to add the latest &lt;strong&gt;Firebase libraries v. 11.2.0&lt;/strong&gt; you have to add the same repo as &lt;a href="https://developers.google.com/android/guides/releases#august_2017_-_version_1120" rel="nofollow noreferrer"&gt;described here&lt;/a&gt;.&lt;/p&gt;
+[K4]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Error:Execution failed for task ':app:processDebugManifest'. &gt; Manifest merger failed
+A: &lt;p&gt;There are some mistakes:&lt;/p&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of Firebase and Google Play Services&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;Change:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:10.0.1'
+compile 'com.google.android.gms:play-services:10.0.1'
+compile 'com.google.firebase:firebase-storage:10.0.1'
+compile 'com.google.firebase:firebase-auth:11.0.1'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;using the latest version:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.google.firebase:firebase-database:11.4.2'
+compile 'com.google.android.gms:play-services:11.4.2'
+compile 'com.google.firebase:firebase-storage:11.4.2'
+compile 'com.google.firebase:firebase-auth:11.4.2'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use the &lt;strong&gt;same version of support libraries&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:recyclerview-v7:26.1.0'
+compile 'com.android.support:appcompat-v7:26.1.0'
+compile 'com.android.support:support-v4:26.1.0'
+compile 'com.android.support:support-compat:26.1.0'
+compile 'com.android.support:cardview-v7:26.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FirebaseUI has dependency on a fixed version of firebase libraries.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Check &lt;a href="https://github.com/firebase/FirebaseUI-Android" rel="nofollow noreferrer"&gt;the table&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;For convenience, here are some examples:&lt;/p&gt;
+&lt;pre&gt;&lt;code</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1355,10 +1976,21 @@
 This configuration should resolve your issue, allowing the AVPlayer to successfully handle the audio streaming through FFmpeg.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1418,13 +2050,52 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific method or best practice for converting a string to a RenderFragment in Blazor. They do not provide any information on the topic or clarify whether the approach you are using (`RenderFragment fragm = @&amp;lt;text&amp;gt;@myString&amp;lt;/text&amp;gt;;`) is the best way to achieve this. Therefore, I cannot provide guidance based on the provided context.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific method or best practice for converting a string to a RenderFragment in Blazor. They do not provide any information on the topic or clarify whether the approach you are using (`RenderFragment fragm = @&amp;lt;text&amp;gt;@myString&amp;lt;/text&amp;gt;;`) is the best way to achieve this. Therefore, I cannot provide guidance.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+.toString());
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+ dynamically in the code.&lt;/p&gt;
+&lt;p&gt;After all, it doesn't need to be specified in the C# source code -- can it be done?&lt;/p&gt;
+&lt;p&gt;Cheers,&lt;/p&gt;
+[K3]
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Will get you :&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;string 'I. NEED. ISOLATION' (length=18)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Note the only thing I changed compared to your proposed code is the regex delimiter ;-)&lt;/p&gt;
+&lt;br&gt;
+And, using a character that's not present in the HTML string, I don't have anything to escape -- especially, I don't have to escape all the `/`s -- which means the regex is far more easy to both write, read, and understand.
+[K4]
+ e.g. &lt;code&gt;coalesce(1)&lt;/code&gt; &lt;em&gt;(OK, 1 is a bit caricatural, but you see the point)&lt;/em&gt;.&lt;/p&gt;
+[K5]
+Q: Java - converting string to a List
+A: &lt;p&gt;With the additional servlet/JSP context you provided, it seems that the &lt;em&gt;real&lt;/em&gt; mistake in your code is the use of &lt;code&gt;request.getParameter&lt;/code&gt; in the JSP page: that method indeed returns a &lt;code&gt;String&lt;/code&gt;, and you can't &lt;em&gt;convert&lt;/em&gt; a &lt;code&gt;String&lt;/code&gt; in a &lt;code&gt;List&lt;/code&gt;, not with a cast, not even with any other operation allowed by the language or the data structures. You may &lt;em&gt;insert&lt;/em&gt; a &lt;code&gt;String&lt;/code&gt; into a &lt;code&gt;List&lt;/code&gt;, using one of the methods already suggested (or &lt;em&gt;transform&lt;/em&gt; a &lt;code&gt;List&lt;/code&gt; into a &lt;code&gt;String&lt;/code&gt; using other methods), but judging from the code that's not what you need.&lt;/p&gt;
+&lt;p&gt;In the servlet code, you set the &lt;code&gt;styles&lt;/code&gt; &lt;em&gt;attribute&lt;/em&gt; to the &lt;code&gt;List&lt;/code&gt; containing the beer brands. So, to get that &lt;code&gt;List&lt;/code&gt; back, you need to invoke &lt;code&gt;request.getAttribute&lt;/code&gt; instead of &lt;code&gt;getParameter&lt;/code&gt;. The &lt;code&gt;getAttribute&lt;/code&gt; methods returns an &lt;code&gt;Object&lt;/code&gt;, which really is a &lt;code&gt;List&lt;/code&gt;, and you know that because you have set it to be as such, so in this case a cast is exactly the operation that is needed to get back the value with its original type. In code, this means&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;List styles = (List) request.getAttribute("styles");
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;in your JSP, in place of the line that got you troubles.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1460,13 +2131,100 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specific context of integrating Blazor Server with OpenIdDict and the proper handling of access tokens for introspection. They focus on AngularJS, CORS, and general API authentication with JWT, among other unrelated topics. Therefore, I cannot provide a concrete answer based on the available context.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] the specific context of integrating Blazor Server with OpenIdDict and the proper handling of access tokens for introspection. They focus on AngularJS, CORS, and general API authentication with JWT, among other unrelated topics. Therefore, I cannot provide a concrete answer.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: AngularJS $http, CORS and Basic authentication with Jersey
+A: &lt;p&gt;So here's what's going on. The &lt;a href="https://developer.mozilla.org/en-US/docs/Glossary/Preflight_request" rel="nofollow noreferrer"&gt;CORS Preflight request&lt;/a&gt; is an &lt;code&gt;OPTIONS&lt;/code&gt; request. This request happens &lt;em&gt;prior&lt;/em&gt; to the real request. It checks with the server to see if the request is allowed. In response to the preflight request, the server should send back the &lt;code&gt;Access-Control-X-X&lt;/code&gt; headers like you are in your &lt;code&gt;getAllUserLogInHistoryAngular&lt;/code&gt; method.&lt;/p&gt;
+&lt;p&gt;So what is happening in your case during the preflight, is that it hits the Basic Auth filter and automatically gets rejected without adding the CORS response headers. Your putting the CORS response headers in the resource method does nothing and is useless. Generally the CORS should be handled in a filter so it handles all requests prior to hitting the resource methods.&lt;/p&gt;
+&lt;p&gt;Here's what you should do. Just like you did for Basic Auth, use a &lt;code&gt;ContainerRequestFilter&lt;/code&gt; to handle the CORS. You want this filter to be called before the Auth filter because the CORS preflight doesn't care about authentication and it will not send the authentication credentials with the request. In this filter, you should check to see if it is a CORS preflight request. Generally this can be done by checking for an &lt;code&gt;OPTIONS&lt;/code&gt; method and he presence of the &lt;code&gt;Origin&lt;/code&gt; header. If it is a preflight, then abort the request and add the CORS headers in a &lt;code&gt;ContainerResponseFilter&lt;/code&gt;. It might look something like&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;@Provider
+@PreMatching
+public class CorsFilter implements ContainerRequestFilter, ContainerResponseFilter {
+    @Override
+    public void filter(Container
+[K2]
+Q: Pass authentication information from MVC into angular
+A: &lt;p&gt;I can share what I do in my own apps, and although I am using ui-router, the same technique &lt;a href="https://stackoverflow.com/questions/19937751/angular-how-use-one-resolve-for-all-the-routes-of-my-application/19938307#19938307"&gt;can easily be applied to the built in router&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Basic logical workflow:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;Automatically add a &lt;code&gt;resolve&lt;/code&gt; to every route that fetches the user's current auth status and caches it.&lt;/li&gt;
+&lt;li&gt;Check if route requires authentication, and reject if user is not logged in, otherwise allow to proceed normally.&lt;/li&gt;
+&lt;li&gt;On &lt;code&gt;$routeChangeError&lt;/code&gt; (or something similar) check to see what action to perform.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;The advantage of this is it allows you to have a great deal of flexibility with regard to providing a nice client side experience with security.&lt;/p&gt;
+&lt;h2&gt;Adding Credentials to Every Route:&lt;/h2&gt;
+&lt;pre&gt;&lt;code&gt;let originalStateFunction = $stateProvider.state;
+$stateProvider.state = function (state, config) {
+  //
+  // The "allowAnonymous" is something we added manually
+  // This will become important later because we might have
+  // routes that don't require authentication, like say
+  // the login page
+  //
+  if (angular.isDefined(config) &amp;amp;&amp;amp; !config.allowAnonymous) {
+      _.defaults(config.resolve || (config.resolve = {}), {
+          /*@ngInject*/
+          userSession: function userSessionSecurityCheck($q, sessionService) {
+              let def = $q.defer();        
+              sessionService.getSession()
+                .then(session =&amp;gt; {
+                   if(!session.isAuthenticated){
+                      def.reject({
+                        error:'AUTHENTICATION_REQUIRED'
+                      });
+                   }
+                });
+              return def.promise;
+[K3]
+Q: Get data from access token
+A: &lt;p&gt;Use the JWT ruby gem&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;x = Net::HTTP.post_form(URI.parse('http://somesite.com/get_token'), params)
+@res = ActiveSupport::JSON.decode(x.body) 
+id_token = @res['id_token']
+id_data = JWT.decode id_token, 'secret', false
+&lt;/code&gt;&lt;/pre&gt;
+[K4]
+Q: Migrating expressjs app to serverless - express-session problem
+A: &lt;p&gt;One solution is to use the JSON Token. The session are stored directly on the client side.&lt;/p&gt;
+&lt;p&gt;In theory, at first connexion, you set a token for the session, and send it to the client.&lt;/p&gt;
+&lt;p&gt;Each time the user call the Api, you send the JSON Token. On the server side, you fill it with the data you need (it's an object)... And send it again to the client...&lt;/p&gt;
+&lt;p&gt;There are a lot of implementation of this process, and with JWT: &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://serverless.com/blog/strategies-implementing-user-authentication-serverless-applications/" rel="nofollow noreferrer"&gt;https://serverless.com/blog/strategies-implementing-user-authentication-serverless-applications/&lt;/a&gt;
+&lt;a href="https://ponyfoo.com/articles/json-web-tokens-vs-session-cookies" rel="nofollow noreferrer"&gt;https://ponyfoo.com/articles/json-web-tokens-vs-session-cookies&lt;/a&gt;
+....&lt;/p&gt;
+&lt;hr&gt;
+&lt;p&gt;According to Amazon, the best approch to manage session is to set it in a third party, as you tried you said...&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://aws.amazon.com/fr/blogs/compute/going-serverless-migrating-an-express-application-to-amazon-api-gateway-and-aws-lambda/" rel="nofollow noreferrer"&gt;https://aws.amazon.com/fr/blogs/compute/going-serverless-migrating-an-express-application-to-amazon-api-gateway-and-aws-lambda/&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Extract : &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;* Storing local state is unreliable due to automatic scaling. Consider going stateless (using REST),
+* or use an external state store (for MongoDB, you can use the connect-mongo package)
+app.use(session({ secret: process
+[K5]
+Q: MEAN-Stack - UnauthorizedError: No authorization token was found
+A: &lt;p&gt;The route is protected from your backend aka your server.js
+your server which im assuming is being run on port 3000 is protected unless you provide a token on your indicated method to which your authorizer will extract from usually its the headers.&lt;/p&gt;
+&lt;p&gt;to over come this i recommend getting a token from aka do a request that will produce one, usually there's a route setup and you can use postman to post data to get a token, once you have a token use postman to send a get request to that same route you couldn't get access to but make sure you add the header authorization or w.e it's looking for the token on. then you'll get access.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1536,10 +2294,123 @@
 This solution aligns with the concept of manipulating individual elements in jQuery, ensuring that each field gets the correct class based on its individual content.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: jquery giving TypeError getting elements from wrapped set
+A: &lt;p&gt;&lt;code&gt;addClass&lt;/code&gt; is a jQuery method. It can only be called on jQuery objects. When you call &lt;code&gt;[0]&lt;/code&gt; or &lt;code&gt;.get(0)&lt;/code&gt; on your jQuery object, you are fetching the underlying DOM element. That object doesn't support the jQuery methods.&lt;/p&gt;
+&lt;p&gt;You should call &lt;code&gt;addClass&lt;/code&gt; on the jQuery object itself:&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;img[alt].addClass('my-new-class');&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;If you only want to add a class to the first image with an &lt;code&gt;alt&lt;/code&gt; attribute, you could change the jQuery selector to &lt;code&gt;$('img[alt]:first')&lt;/code&gt;.&lt;/p&gt;
+[K2]
+Q: Jquery check if i tag has a class and replace it
+A: &lt;p&gt;First of all, make sure your class names do NOT have spaces. Spaces in &lt;code&gt;class="a b"&lt;/code&gt; actually means 2 separate classes, a and b, not a class "a b". Also as others have mentioned, IDs should be unique. So with code:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;ul class="list-inline recommended-logo"&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-1" class="first_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;First class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-2" class="second_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Second class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+    &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-3" class="third_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Third, class&amp;lt;/span&amp;lt;/li&amp;gt;
+   &amp;lt;li&amp;gt;&amp;lt;i id="icon-changer-4" class="fourth_class"&amp;gt;&amp;lt;/i&amp;gt;&amp;lt;span&amp;gt;Four class&amp;lt;/span&amp;gt;&amp;lt;/li&amp;gt;
+&amp;lt;/ul&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;You can select by class (with a .) and replace easily:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$('.first_class').removeClass('first_class').addClass('fifth_class')
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;will take everything with the class "first_class" and replace it with "fifth_class".&lt;/p&gt;
+&lt;p&gt;I stand by my original code as listed above. But looking at the edits to the question, the problem is apparently using jQuery to select on ID when IDs are repeated - the first  So &lt;strong&gt;ignore&lt;/
+[K3]
+Q: Jquery Burger Menu wont apply class correctly
+A: &lt;p&gt;The problem is in the css rule ,&lt;/p&gt;
+&lt;p&gt;Instead of &lt;strong&gt;&lt;code&gt;header nav ul .open&lt;/code&gt;&lt;/strong&gt; set it to  &lt;strong&gt;&lt;code&gt;header nav ul.open&lt;/code&gt;&lt;/strong&gt; (remove space between &lt;code&gt;ul&lt;/code&gt; and &lt;code&gt;.space&lt;/code&gt; class) , the first  search for element insude the ul that has .open class , the second the ul that has .open class , that's the difference &lt;/p&gt;
+&lt;p&gt;See below snippet &lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="true" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code snippet-currently-hidden"&gt;
+&lt;pre class="snippet-code-js lang-js prettyprint-override"&gt;&lt;code&gt;$(document).ready(function() {
+  $(".burger-nav").on("click", function() {
+      $("header nav ul").toggleClass("open");
+  });
+});&lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;@media screen and (max-width: 680px) {
+  .burger-nav {
+    display: block;
+    height: 30px;
+    width:40px;
+    background: url(https://cdn.css-tricks.com/wp-content/uploads/2012/10/threelines.png) no-repeat 98% center;
+    background-color: blue;
+    background-size: 50px;
+    cursor:pointer;
+  }
+  header .navwrap{
+    padding:0;
+    width:100%;
+  }
+  header nav ul {
+    overflow:hidden;
+    background: #505050;
+    height: 0 ;
+  }
+  header nav ul.open {
+    height: auto;
+  }
+  header nav ul li {
+    float: none;
+    text-align: left;
+    width: 100%;
+    margin: 
+[K4]
+Q: Use of a class inside another class
+A: &lt;p&gt;Use the class which you have given to the span itself.&lt;/p&gt;
+&lt;p&gt;&lt;div class="snippet" data-lang="js" data-hide="false" data-console="true" data-babel="false"&gt;
+&lt;div class="snippet-code"&gt;
+&lt;pre class="snippet-code-css lang-css prettyprint-override"&gt;&lt;code&gt;.description p span {
+  font-style: italic;
+}
+.description .cor {
+  font-style: normal;
+  color: red;
+} &lt;/code&gt;&lt;/pre&gt;
+&lt;pre class="snippet-code-html lang-html prettyprint-override"&gt;&lt;code&gt;&amp;lt;div class="description"&amp;gt;
+  &amp;lt;p&amp;gt;This recipe is from one of my &amp;lt;span class="cor"&amp;gt;favorite&amp;lt;/span&amp;gt; cakes out there, really &amp;lt;span&amp;gt;delicious&amp;lt;/span&amp;gt;...check it out below&amp;lt;/p&amp;gt;
+&amp;lt;/div&amp;gt;&lt;/code&gt;&lt;/pre&gt;
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;/p&gt;
+[K5]
+Q: nested jquery $.each repeating iteration issue
+A: &lt;p&gt;You could return the newly created &lt;code&gt;.table-list&lt;/code&gt; using &lt;code&gt;.appendTo&lt;/code&gt; (rather than &lt;code&gt;.append&lt;/code&gt;) so that it can be appended to:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;function getList() {
+ $.getJSON(&amp;quot;src/list.json&amp;quot;, function(data) {
+  $.each(data, function( key, fax ) {
+      const faxItem = this;
+      displayOnDom.append(`&amp;lt;div id=faxPlan-${faxItem.id} class=&amp;quot;pricing-table flex-item ${faxItem.recommended ? 'recommended' : ''}&amp;quot;&amp;gt;
+        &amp;lt;h3 class=&amp;quot;pricing-title&amp;quot;&amp;gt;${faxItem.title}&amp;lt;/h3&amp;gt;
+        &amp;lt;div class=&amp;quot;price&amp;quot;&amp;gt;${faxItem.price_per_month}&amp;lt;sup&amp;gt;/ month&amp;lt;/sup&amp;gt;&amp;lt;/div&amp;gt;
+        ${faxItem.button ? `&amp;lt;p class=&amp;quot;rounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;` : `&amp;lt;p class=&amp;quot;norounded&amp;quot;&amp;gt;${faxItem.button_text}&amp;lt;/p&amp;gt;`}
+        `);
+      var tablelist = $('&amp;lt;div class=&amp;quot;table-list&amp;quot;&amp;gt;&amp;lt;/div&amp;gt;').appendTo(displayOnDom);
+      $.each(fax.features, function( key, list ) {
+        tablelist.append(`&amp;lt;p&amp;gt;${list.title}&amp;lt;span&amp;gt;${list.list}&amp;lt;/span&amp;gt;&amp;lt;/p&amp;gt;`)
+      })
+   })   
+ });
+}
+&lt;/code&gt;&lt;/pre&gt;
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1578,13 +2449,85 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover a specific approach to resolve the issue of "missing necessary objects" and "remote: error: refs/pull/904/head does not point to a valid object!" mentioned in your problem. Therefore, I'm unable to provide a solution based on the given context.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] a specific approach to resolve the issue of "missing necessary objects" and "remote: error: refs/pull/904/head does not point to a valid object!" mentioned in your problem. Therefore, I'm unable to provide a solution.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: remote: fatal: fsck error in packed object when pushing oh-my-zsh repo to new remote
+A: &lt;p&gt;&lt;a href="https://gitlab.com/gitlab-org/gitaly/issues/787" rel="nofollow noreferrer"&gt;In theory, this was already fixed at GitLab.&lt;/a&gt;  Why it is showing up for you, I have no idea.&lt;/p&gt;
+&lt;p&gt;The problem here is that &lt;code&gt;https://github.com/robbyrussell/oh-my-zsh&lt;/code&gt; itself is (somewhat) broken.  This has nothing to do with anything you did.  Meanwhile, your &lt;code&gt;gitlab.com&lt;/code&gt; service is configured to be ultra-strict.  This &lt;em&gt;also&lt;/em&gt; &lt;strong&gt;probably&lt;/strong&gt; has nothing to do with anything you did—but you'll need to change it, or else give up on the idea of sending &lt;em&gt;this&lt;/em&gt; repository to &lt;code&gt;gitlab.com&lt;/code&gt;.  (Or, perhaps your best bet, get them to note that their fix has un-fixed itself.)&lt;/p&gt;
+&lt;p&gt;If you clone the URL above and run &lt;code&gt;git fsck&lt;/code&gt; on your own clone, you'll see this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;$ git fsck
+Checking object directories: 100% (256/256), done.
+warning in tree 2b7227859263b6aabcc28355b0b994995b7148b6: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree a18c4d13c2a5fa2d4ecd5346c50e119b999b807d: zeroPaddedFilemode: contains zero-padded file modes
+warning in tree 84df066176c8da3fd59b13731a86d90f4f1e5c9d: zeroPaddedFile
+[K2]
+Q: GIT 2nd PUSH is failing
+A: &lt;blockquote&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;Git will not allow you to push changes if our branch is not up to date with the server&lt;/p&gt;
+&lt;p&gt;Once you try to &lt;code&gt;push&lt;/code&gt; your code to the remote repo git verify that your &amp;quot;local&amp;quot; branch has all the latest code from the remote branch. If it see that you are missing some commits it will not let you push the code to the remote.&lt;/p&gt;
+&lt;hr /&gt;
+&lt;h3&gt;How to fix it?&lt;/h3&gt;
+&lt;p&gt;Its very simple - you simply need to pull the changes from the server in one of the following ways:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;# assuming you are on the desired branch
+# update your local server with all the latest code from the server
+# This is an optional command but its a good practice to always be 
+# synchronized with the server
+git fetch --all --prune
+# now pull (pull = fetch + merge) the changes from the server to your branch
+git pull origin &amp;lt;branch name&amp;gt;
+# now your local branch is up to date and contains all the &amp;quot;server&amp;quot; code as well
+# push your changes to the remote branch
+git push origin &amp;lt;branch name&amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+[K3]
+Q: "fatal: strange pathname '-im/somerepo.git' blocked
+A: &lt;p&gt;The leading &lt;code&gt;-&lt;/code&gt; character caused security issues in previous versions of git. It seems your Ubuntu installation contains the fixed Debian version that blocks your fetch attempt. You should rename the repository on BitBucket, and update your local configuration accordingly.&lt;/p&gt;
+&lt;p&gt;&lt;a href="http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2" rel="nofollow noreferrer"&gt;http://marc.info/?l=git&amp;amp;m=150238802328673&amp;amp;w=2&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff" rel="nofollow noreferrer"&gt;https://release.debian.org/proposed-updates/stable_diffs/git_2.11.0-3+deb9u1.debdiff&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: GitHub repository disabled when changing from private to public
+A: &lt;p&gt;Contacted GitHub support and they unlocked the repository. It may have happened because I changed the repo from private to public during their outage. Everything works fine now&lt;/p&gt;
+[K5]
+Q: merging local repo with github repo is resulting in a fatal error
+A: &lt;p&gt;Errors tell that your local branch is behind from master.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;Updates were rejected because the tip of your current branch is behind&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;1) Try &lt;code&gt;git pull origin master --rebase&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;if it does not work then local and remote branch, not in sync.
+you have to first sync your local master branch with remote master.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;follow following steps:&lt;/strong&gt;&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;copy your new commit hash which you recently commit.&lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git fetch origin&lt;/code&gt; &lt;/li&gt;
+&lt;li&gt;run &lt;code&gt;git reset --hard origin/master&lt;/code&gt; # to sync your
+local master with remoter master &lt;/li&gt;
+&lt;li&gt;cherry-pick your commit: &lt;code&gt;git cherry-pick your_commit_hash&lt;/code&gt;&lt;/li&gt;
+&lt;li&gt;&lt;code&gt;git push origin master&lt;/code&gt; # to push your commit
+Let me know if it still not resolved.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Thanks!&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1616,18 +2559,62 @@
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>To develop OpenGL 4.x applications on Linux, you can use several commonly used libraries:
-1. **GLEW (OpenGL Extension Wrangler Library)**: This library is used to manage OpenGL extensions and is a good choice for accessing OpenGL APIs on Linux. GLEW allows you to utilize modern OpenGL features efficiently and is cross-platform, meaning you can use it without issues when transitioning from Windows to Linux .
-2. **GLFW (Graphics Library Framework)**: GLFW is another cross-platform library that helps with managing OpenGL contexts, windows, and inputs. Just like GLEW, it should work seamlessly on Linux .
-3. **Mesa**: For implementing OpenGL, you can also use Mesa3D, which is an open-source OpenGL implementation for Linux. It supports up to OpenGL 4.x, although the availability can depend on the specific graphics drivers and the version of Mesa you are using . It’s important to note that Mesa may have some limitations compared to proprietary drivers from AMD or NVIDIA but should work well for many use cases .
-4. **Vendor-specific drivers**: If you're targeting specific hardware, such as AMD or NVIDIA graphics cards, their proprietary drivers may provide even better performance and support for OpenGL 4.x features. They typically come as closed-source implementations and may provide a more feature-complete support than Mesa .
-Since you are interested in a "pure" C++ solution and wish to avoid frameworks like Qt, GLEW and GLFW would be suitable choices for your development on Linux. The retrieved sources indicate that both libraries are well-suited for handling OpenGL tasks cross-platform, including Linux, without additional dependencies . 
-For installation, you would typically install these libraries using your package manager, such as `apt` or `dnf`, depending on the Linux distribution you are using .</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+1. **GLEW (OpenGL Extension Wrangler Library)**: This library is used to manage OpenGL extensions and is a good choice for accessing OpenGL APIs on Linux. GLEW allows you to utilize modern OpenGL features efficiently and is cross-platform, meaning you can use it without issues when transitioning from Windows to Linux.
+2. **GLFW (Graphics Library Framework)**: GLFW is another cross-platform library that helps with managing OpenGL contexts, windows, and inputs. Just like GLEW, it should work seamlessly on Linux.
+3. **Mesa**: For implementing OpenGL, you can also use Mesa3D, which is an open-source OpenGL implementation for Linux. It supports up to OpenGL 4.x, although the availability can depend on the specific graphics drivers and the version of Mesa you are using. It’s important to note that Mesa may have some limitations compared to proprietary drivers from AMD or NVIDIA but should work well for many use cases.
+4. **Vendor-specific drivers**: If you're targeting specific hardware, such as AMD or NVIDIA graphics cards, their proprietary drivers may provide even better performance and support for OpenGL 4.x features. They typically come as closed-source implementations and may provide a more feature-complete support than Mesa.
+Since you are interested in a "pure" C++ solution and wish to avoid frameworks like Qt, GLEW and GLFW would be suitable choices for your development on Linux. Both libraries are well-suited for handling OpenGL tasks cross-platform, including Linux, without additional dependencies. 
+For installation, you would typically install these libraries using your package manager, such as `apt` or `dnf`, depending on the Linux distribution you are using.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Is it possible to use OpenGL 4.5 features with latest mesa libraries?
+A: &lt;blockquote&gt;
+  &lt;p&gt;I want to use latest OpenGL features on Ubuntu. And I have installed mesa-common-dev but as far as I understand mesa does not support OpenGL 4.5 features. &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;All that matters is, that your actual OpenGL implementation supports the profile you want. The Linux ABI on OpenGL is pinned to OpenGL-1.2 (LSB5 has been released recently, so expect upcoming  distribution releases to follow it, which bumped it to OpenGL-2.1).&lt;/p&gt;
+&lt;p&gt;Anything that goes beyond the ABI requirements is done through the extension mechanism. I.e. use load function pointers through &lt;em&gt;…GetProcAddress&lt;/em&gt; and introduce new tokens with a &lt;code&gt;glext.h&lt;/code&gt;. This processes has been repacked into OpenGL extension wrapper-loader libraries like GLEW.&lt;/p&gt;
+&lt;p&gt;The stuff mesa-common-dev provides is what's written down in the Linux LSB ABI specs… in a vendor neutral way, so you can compile your program using mesa-common-dev stuff, but it will work with the NVidia or AMD/ATI drivers as well.&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;Also how can I use OpenGL via hardware without any API ? &lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;By definition you can't. OpenGL is an API. If you remove the API you remove OpenGL. If your intention is working the naked GPU on the bare metal, well, that would boil down to writing a full driver. In a few weeks/months Vulkan will be released and this gets you much closer to the GPU than OpenGL.&lt;/p&gt;
+[K2]
+Q: I need openGl 2.0 but my graphic card support 1.5
+A: &lt;p&gt;It's possible that updating drivers might help some, but probably won't make that jump. Otherwise, you could use something like &lt;a href="http://www.mesa3d.org/" rel="nofollow noreferrer"&gt;Mesa3D&lt;/a&gt;, which does the rendering in software. It can be slow, but does support up through OpenGL 2.1 (including shaders), if memory serves.&lt;/p&gt;
+[K3]
+Q: What percentage of Windows boxes have OpenGL support
+A: &lt;p&gt;As I recall, Windows XP comes with 1.1 support out of the box. Vista upgrades this to 1.5. So you can at least count on those as an absolute minimum.&lt;/p&gt;
+&lt;p&gt;Apart from that, the GPU drivers from pretty much any vendor gives you &lt;em&gt;at least&lt;/em&gt; 2.0 support.&lt;/p&gt;
+&lt;p&gt;But if I were you, I'd reconsider DirectX. I don't know what you hate about it, but it does have some advantages. The tool support is vastly better (ie, there are tools available. And PIX is nothing short of amazing), the API is up to date, and well designed, rather than accumulated over 20 years of a committee working at cross purposes, and if this is limited to Windows anyway, cross-platform doesn't really matter. (On the other hand, of course, if you do need cross-platform capabilities, it doesn't really matter what else DirectX can offer, it won't deliver that one killer feature)&lt;/p&gt;
+[K4]
+Q: Starting to learn OpenGL. On modern Linux, how are all these concepts related?
+A: &lt;p&gt;OpenGL is an interface.  To use it, you need an implementation.  There are many implementations of OpenGL.  Because each implementation is different, your program will behave differently when you run it with different implementations, even though your program is the same.  A typical OpenGL implementation with a hardware renderer will consist of some code that runs in user space (a dynamic library), code that runs in the kernel (the device driver), code that runs in your X.org server (the DDX driver), and code that runs on the graphics card itself (the firmware).  That's four different pieces of code!&lt;/p&gt;
+&lt;p&gt;AMD and nVidia provide proprietary OpenGL implementations for Linux.  These implementations have closed-source drivers which &lt;a href="https://unix.stackexchange.com/questions/118116/linux-what-is-a-tainted-kernel"&gt;&lt;em&gt;taint the kernel,&lt;/em&gt;&lt;/a&gt; which means that if something goes wrong, the Linux developers can't help you.  They support recent OpenGL versions (e.g. 4.5, if your hardware is capable) with the full compatibility profile support.&lt;/p&gt;
+&lt;p&gt;Mesa provides an open-source OpenGL implementation for Linux.  This implementation can use the Noveau or Radeon open-source drivers, which do not taint the kernel.  Mesa also has a software implementation, called llvmpipe, which runs on your CPU only and doesn't need drivers.  It's impressively fast for what it is, but it is much slower than even an outdated hardware implementation.  Mesa recently started supporting OpenGL 4.x series, but it will take some time before it filters through distro release cycles, so you're more likely to see OpenGL 3.3--and that's only for the core profile, you're limited to 3.0 with the compatibility profile (similar to how it works on
+[K5]
+ OS X).&lt;/p&gt;
+&lt;p&gt;Because Mesa developers have limited access to documentation about the graphics cards, and limited development resources, the Mesa implementation on your AMD or nVidia card is usually slower than the vendor's implementation, and it usually supports fewer OpenGL extensions.  However, the Mesa implementation is very solid, it doesn't taint your kernel, and some of the Mesa implementations are even Valgrind-clean.&lt;/p&gt;
+&lt;p&gt;Installing OpenGL just means installing an OpenGL implementation on your system (you know, with &lt;code&gt;dnf&lt;/code&gt; or &lt;code&gt;apt&lt;/code&gt; or whatever).  This usually means a choice between the vendor implementation and the Mesa implementation... except for Intel integrated graphics, where Mesa &lt;em&gt;is&lt;/em&gt; the vendor implementation.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1656,7 +2643,7 @@
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>The issue you are encountering with the BlackBerry application description text exceeding 255 characters is likely related to the constraints imposed by the Eclipse plugin for BlackBerry development. In the BlackBerry ecosystem, especially in earlier versions like the BlackBerry JRE 5.0.0, there are often strict limits on the length of certain fields in the BlackBerry_App_Descriptor.xml file.
-In your case, since the application description works without errors when it's 255 characters or fewer, but fails when it exceeds that limit, it suggests that the plugin enforces this character limit. While this issue might not have a straightforward solution directly cited from your provided contexts, I can recommend the following approaches to resolve it:
+In your case, since the application description works without errors when it's 255 characters or fewer, but fails when it exceeds that limit, it suggests that the plugin enforces this character limit. While this issue might not have a straightforward solution directly cited I can recommend the following approaches to resolve it:
 1. **Shorten the Description**: As a temporary workaround, consider shortening your application description to 255 characters or fewer until you can find a more permanent solution.
 2. **Check Updates**: Ensure you are using the most updated version of the BlackBerry development tools, as there may be patches or updates that address this limitation.
 3. **Consult BlackBerry Documentation**: Look at the latest BlackBerry development documentation or forums for any additional advice on this specific constraint.
@@ -1664,10 +2651,55 @@
 These steps should help you manage the character limit issue while you work towards a more scalable solution.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Blackberry @Override notation error
+A: &lt;p&gt;Blackberry development is built on top of j2me, which has the language features of Java 1.3.  This means it doesn't support annotations. You can remove the @Override annotations and your code will work.  Remember these are optional although recommended anyways.&lt;/p&gt;
+&lt;p&gt;What I do, is write //@Override instead. When/If annotations are added in the future it will be easy to do a regex replace and remove the comment marks.&lt;/p&gt;
+[K2]
+Q: java.io.UnsupportedEncodingException: ISO-8859-8, text/xml
+A: &lt;p&gt;&lt;code&gt;ISO-8859-8&lt;/code&gt; is not one of the &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/StandardCharsets.html" rel="nofollow noreferrer"&gt;standard charsets&lt;/a&gt; that Java &lt;em&gt;needs&lt;/em&gt; to support, i.e. which are guaranteed to be found (unless you have a corrupted installation).&lt;/p&gt;
+&lt;p&gt;In your case, the difference seems to be in the Windows 10 environment. I would check first that it has support for &lt;code&gt;ISO-8859-8&lt;/code&gt; (I don't know how though, I'm not a Windows user). It may need to be installed/enabled separately.&lt;/p&gt;
+&lt;p&gt;If you're &lt;strong&gt;certain&lt;/strong&gt; that your Windows 10 does support that encoding, then it's a problem with Java not being able to make the connection between the two, and you'll probably have to delve into &lt;a href="https://docs.oracle.com/javase/8/docs/api/java/nio/charset/spi/CharsetProvider.html" rel="nofollow noreferrer"&gt;charset providers&lt;/a&gt;, but let's hope you don't have to go there.&lt;/p&gt;
+[K3]
+Q: The encoding 'UTF-8' is not supported by the Java runtime
+A: &lt;p&gt;Most probably someone put a catch() expecting to have only unsupported encoding exceptions, so he used the appropriate message. But he has used too wide exception specification (e.g. catch( Exception ex ) ), so when at runtime he's got something else (non-valid XML, NPE, ... ) the message became misleading.&lt;/p&gt;
+[K4]
+Q: Does Blackberry support Android OS
+A: &lt;p&gt;Although Android and Blackberry both use Java, they expose very different application APIs to developers.  So I don't think it is possible to run Android apps on a Blackberry - YET.  RIM has already announced that they are planning on supporting Android apps on the upcoming Blackberry Playbook tablet.&lt;/p&gt;
+[K5]
+Q: Eclipse - "Incompatible JVM. Version 1.8.0_261 of the JVM is not suitable for this product. Version: 11 or greater is required"
+A: &lt;p&gt;For Ubuntu users, refer to the answer &lt;a href="https://stackoverflow.com/a/64049648/14489697"&gt;https://stackoverflow.com/a/64049648/14489697&lt;/a&gt; by howlger. Add the following lines in file &lt;code&gt;eclipse.ini&lt;/code&gt; before &lt;code&gt;-vmargs&lt;/code&gt;:&lt;/p&gt;
+&lt;pre class="lang-none prettyprint-override"&gt;&lt;code&gt;-vm
+/usr/lib/jvm/adoptopenjdk-14-openj9-amd64/bin/java
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Above is the Java install location. Change this according to yours.&lt;/p&gt;
+&lt;p&gt;I'm using,&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Eclipse IDE for Enterprise Java Developers (includes Incubating components)&lt;/li&gt;
+&lt;li&gt;Version: 2020-12 (4.18.0)&lt;/li&gt;
+&lt;li&gt;Build id: 20201210-1552&lt;/li&gt;
+&lt;li&gt;OS: Linux, v.5.4.0-42-generic, x86_64 / gtk 3.22.30&lt;/li&gt;
+&lt;li&gt;Java version: 14.0.2&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1768,10 +2800,155 @@
 If you still face issues, check the scikit-learn version you are using, as the method and its availability can depend on the version.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: How to get the coefficients from RFE using sklearn?
+A: &lt;pre&gt;&lt;code&gt;from sklearn.linear_model import LogisticRegression
+from sklearn.feature_selection import RFE
+reg = LogisticRegression()
+rfe = RFE(reg, no of features u want to select)
+rfe.fit(X, Y)
+print(rfe.support_)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;you will get to know which features are important and its a better way of looking it.&lt;/p&gt;
+[K2]
+    #the rest in this function are as they were before, beginning with:
+    for new_values in grid:
+        X_eval = X.copy()
+        ....
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Then comment out the first 20 lines of the definition of &lt;code&gt;partial_dependence&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def partial_dependence(estimator, X, features, response_method='auto',
+                   percentiles=(0.05, 0.95), grid_resolution=100,
+                   method='auto'):
+    ... (skipping docstring)
+    # if not (is_classifier(estimator) or is_regressor(estimator)):
+    #     raise ValueError(
+    #         "'estimator' must be a fitted regressor or classifier."
+    #     )
+    # 
+    # if isinstance(estimator, Pipeline):
+    #     # TODO: to be removed if/when pipeline get a `steps_` attributes
+    #     # assuming Pipeline is the only estimator that does not store a new
+    #     # attribute
+    #     for est in estimator:
+    #         # FIXME: remove the None option when it will be deprecated
+    #         if est not in (None, 'drop'):
+    #             check_is_fitted(est)
+    # else:
+    #     check_is_fitted(estimator)
+    # 
+    # if (is_classifier(estimator) and
+    #         isinstance(estimator.classes_[0], np.ndarray)):
+    #     raise ValueError(
+    #         'Multiclass-multioutput estimators are not supported'
+    #     )
+    #The rest of the function continues as it was:
+    # Use check_array only on lists and other non-array-likes / sparse. Do not
+    # convert DataFrame into a NumPy array.
+    if not(hasattr(X, '__array__') or sparse.issparse(X)):
+        X = check_array(X, force_all_finite='allow-nan
+[K3]
+_column_indices
+from sklearn.utils.validation import check_is_fitted
+from sklearn.tree._tree import DTYPE
+from sklearn.exceptions import NotFittedError
+from sklearn.ensemble._gb import BaseGradientBoosting
+from sklearn.ensemble._hist_gradient_boosting.gradient_boosting import (
+    BaseHistGradientBoosting)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;(they had previously been relative paths like &lt;code&gt;from ..utils.extmath import cartesian&lt;/code&gt; etc.)&lt;/p&gt;
+&lt;p&gt;Then, the only functions that are changed are these:&lt;/p&gt;
+&lt;p&gt;From &lt;code&gt;_partial_dependence_brute&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def _partial_dependence_brute(est, grid, features, X, response_method):
+    ... (skipping docstring)
+    averaged_predictions = []
+    # define the prediction_method (predict, predict_proba, decision_function).
+    # if is_regressor(est):
+    #     prediction_method = est.predict
+    # else:
+    #     predict_proba = getattr(est, 'predict_proba', None)
+    #     decision_function = getattr(est, 'decision_function', None)
+    #     if response_method == 'auto':
+    #         # try predict_proba, then decision_function if it doesn't exist
+    #         prediction_method = predict_proba or decision_function
+    #     else:
+    #         prediction_method = (predict_proba if response_method ==
+    #                              'predict_proba' else decision_function)
+    #     if prediction_method is None:
+    #         if response_method == 'auto':
+    #             raise ValueError(
+    #                 'The estimator has no predict_proba and no '
+    #                 'decision_function method.'
+    #             )
+    #         elif response_method == 'predict_proba':
+    #             raise ValueError('The estimator has no predict_proba method.')
+    #         else:
+    #             raise ValueError(
+    #                 'The estimator has no decision_function method.')
+    prediction_method = est.predict
+[K4]
+Q: Optimize this function with numpy (or other vectorization methods)
+A: &lt;p&gt;There's no reason to use loops here. And you really shouldn't use Numba or Cython for this stuff - linear algebra expressions like the one you have are the whole reason behind vectorized operations in Numpy.&lt;/p&gt;
+&lt;p&gt;Since this type of problem is going to pop up again and again if you keep using Numpy, I would recommend getting a basic handle on linear algebra in Numpy. You might find this book chapter helpful:&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.safaribooksonline.com/library/view/python-for-data/9781449323592/ch04.html" rel="nofollow"&gt;https://www.safaribooksonline.com/library/view/python-for-data/9781449323592/ch04.html&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;As for your specific situation: start by creating numpy arrays from your variables:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;import numpy as np
+W = np.array(W)
+p = np.array(p)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Now, your \bar p_i^2 are defined by a dot product. That's easy:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;bar_p_i = p.T.dot(W)
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Note the T, for the transpose, because the dot product takes the sum of the elements indexed by the last index of the first matrix and the first index of the second matrix. The transpose inverts the indices so the first index becomes the last.&lt;/p&gt;
+&lt;p&gt;You H_t is defined by a sum. That's also easy:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;H_T = 1 - bar_p_i.sum()
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Similarly for your H_S:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;H_S = 1 - ((bar_p_i**2).T.dot(W)).sum()
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: how to calculate error part in of fitted line of polyfit to data?
+A: &lt;p&gt;Your variable &lt;code&gt;sstot&lt;/code&gt; is a scalar and will be reset for each iteration of your loop. This means that when you run the following line:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;results = pd.DataFrame({'skills':columns, 'coef': coef, 'error':error, 'error2':sstot}) 
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;The column &lt;code&gt;error2&lt;/code&gt; will be set to scalar value of sstot in the most recent iteration of your for loop, which is why error2 has all the same value.&lt;/p&gt;
+&lt;p&gt;I am guessing that you meant to keep track of sstot for each &lt;code&gt;skill&lt;/code&gt;, so you can create a list called &lt;code&gt;error2, then set the column &lt;/code&gt;error2&lt;code&gt;equal to this list (like the lists you created for&lt;/code&gt;coef&lt;code&gt;and&lt;/code&gt;error`). For example:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;def polyfit(df,columns, degree):
+    coef=[]
+    error=[]
+    error2=[]
+    x = np.array(list(range(0,df.shape[0])))
+    for skill in columns:
+        y=df[skill]
+        y=pd.to_numeric(y)
+        coeffs = np.polyfit(x, y, degree)
+        # Polynomial Coefficients
+        coef.append(coeffs.tolist()[0])
+        # r-squared
+        p = np.poly1d(coeffs)
+        # fit values, and mean
+        yhat = p(x)                         # or [p(z) for z in x]
+        ybar = np.sum(y)/len(y)          # or sum(y)/len(y)
+        ssreg = np.sum((yhat-ybar)**2)   # or sum([ (yihat - ybar)**2 for yihat in yhat])
+        sstot = np</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1833,10 +3010,21 @@
 With this approach, you should be able to get the filename correctly and save the audio file as needed.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1940,10 +3128,112 @@
 By following these steps, you should be able to resolve the issues related to `CardView` and `RecyclerView` not being recognized in your project. If you need to continue using older libraries, ensure that they are compatible with your current configurations, but transitioning to AndroidX is strongly advisable for better future support.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Android gradle Error:(69, 0) Gradle DSL method not found: 'compile()'
+A: &lt;p&gt;Try replacing:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}" compile "com.android.support:appcompat-v7:${config.support}" compile "com.android.support:support-v4:${config.support}" compile "com.android.support:recyclerview-v7:${config.support}" compile "com.android.support:design:${config.support}" compile "com.android.support:cardview-v7:${config.support}" compile "com.android.support:percent:${config.support}" compile "com.google.android.gms:play-services-location:${config.location}" compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;with:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;compile "com.android.support:support-v13:${config.support}"
+compile "com.android.support:appcompat-v7:${config.support}"
+compile "com.android.support:support-v4:${config.support}"
+compile "com.android.support:recyclerview-v7:${config.support}"
+compile "com.android.support:design:${config.support}"
+compile "com.android.support:cardview-v7:${config.support}"
+compile "com.android.support:percent:${config.support}"
+compile "com.google.android.gms:play-services-location:${config.location}"
+compile "com.google.android.gms:play-services-maps:${config.location}"
+&lt;/code&gt;&lt;/pre&gt;
+[K2]
+Q: Android CardView layout broken pre-API 28
+A: &lt;p&gt;You can use &lt;a href="https://github.com/intuit/sdp" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;SDP&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt; - a scalable size unit&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+  implementation 'com.intuit.sdp:sdp-android:1.0.6'
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;strong&gt;FYI&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; &amp;lt;android.support.v7.widget.CardView 
+  xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+  xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+  xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+  android:layout_width=&amp;quot;125dp&amp;quot;
+  android:layout_height=&amp;quot;40dp&amp;quot;
+  android:layout_marginEnd=&amp;quot;8dp&amp;quot;
+  app:cardCornerRadius=&amp;quot;165dp&amp;quot;
+  app:cardElevation=&amp;quot;8dp&amp;quot;
+  app:contentPadding=&amp;quot;8dp&amp;quot;
+  &amp;gt;
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Leads to inconsistency. Different layouts end up hard-coding different font sizes and margins, making the app appear less polished.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;TRY&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;?xml version=&amp;quot;1.0&amp;quot; encoding=&amp;quot;utf-8&amp;quot;?&amp;gt;
+   &amp;lt;android.support.v7.widget.CardView 
+    xmlns:android=&amp;quot;http://schemas.android.com/apk/res/android&amp;quot;
+    xmlns:app=&amp;quot;http://schemas.android.com/apk/res-auto&amp;quot;
+    xmlns:tools=&amp;quot;http://schemas.android.com/tools&amp;quot;
+    android:layout_width=&amp;quot;@dimen/_125sdp&amp;quot;
+    android
+[K3]
+Q: Didn't find class "android.support.v7.widget.CardView"
+A: &lt;p&gt;i try you xml &lt;a href="https://i.sstatic.net/LLLdf.png" rel="nofollow noreferrer"&gt;&lt;img src="https://i.sstatic.net/LLLdf.png" alt="enter image description here"&gt;&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;click on {Change to android.support.v7.widget.CardView}&lt;/p&gt;
+&lt;p&gt;no crashed occurred &lt;/p&gt;
+[K4]
+Q: Error inflating android.support.v7.widget.CardView
+A: &lt;p&gt;At first add &lt;strong&gt;&lt;code&gt;setContentView();&lt;/code&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;override fun onCreate(savedInstanceState: Bundle?) {
+    super.onCreate(savedInstanceState)
+    setContentView(R.layout.activity_main) //missing
+    val recyclerView = findViewById(R.id.contactsView) as RecyclerView
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Use Exact version &lt;strong&gt;&lt;code&gt;App Level&lt;/code&gt;&lt;/strong&gt; &lt;code&gt;build.gradle&lt;/code&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; dependencies {
+       implementation 'com.android.support:cardview-v7:28.0.0'
+       implementation 'com.android.support:recyclerview-v7:28.0.0'
+      }
+&lt;/code&gt;&lt;/pre&gt;
+&lt;h2&gt;FYI&lt;/h2&gt;
+&lt;p&gt;You are using very old versions. If you want to use latest then libraries will not work unless you make the following changes in your app:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Upgrade compileSdkVersion to 28 or later.&lt;/li&gt;
+&lt;li&gt;Update your app to use Jetpack (AndroidX).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;AndroidX replaces the original support library APIs with packages in the androidx namespace. Read official guideline about &lt;a href="https://developer.android.com/jetpack/androidx" rel="nofollow noreferrer"&gt;&lt;strong&gt;&lt;code&gt;AndroidX Overview&lt;/code&gt;&lt;/strong&gt;&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Your &lt;strong&gt;&lt;code&gt;Cardview&lt;/code&gt;&lt;/strong&gt; &amp;amp; &lt;strong&gt;&lt;code&gt;recyclerview&lt;/code&gt;&lt;/strong&gt; will&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt; implementation 'androidx.cardview:cardview:1.0.0'
+ implementation 'androidx.recyclerview:recyclerview:1.1.0'
+&lt;/code&gt;&lt;/pre&gt;
+[K5]
+Q: Android L CardView and RecyclerView
+A: &lt;p&gt;&lt;strong&gt;Can I use these widgets in older versions&lt;/strong&gt; :&lt;/p&gt;
+&lt;p&gt;Yes you can. Those can be supported from API level = 7.&lt;/p&gt;
+&lt;p&gt;To use this in android studio add bellow line in your app build.gradle file.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Like :&lt;/strong&gt; &lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;dependencies {
+....
+compile 'com.android.support:cardview-v7:21.0.+'
+compile 'com.android.support:recyclerview-v7:21.0.+'
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;}&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2039,10 +3329,21 @@
 Feel free to ask more questions if you need further clarification or assistance!</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2091,10 +3392,87 @@
 If you troubleshoot these aspects and the issue persists, consider providing more detailed logs or messages produced during the rendering of your R Markdown file for further assistance.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Scraping Wikipedia with R to make a list and a data frame
+A: &lt;p&gt;A possibility is to use regular expressions. I've never done that with R but the library stringr seems to be recommended:
+&lt;a href="https://stackoverflow.com/questions/2192316/extract-a-regular-expression-match-in-r-version-2-10"&gt;Extract a regular expression match in R version 2.10&lt;/a&gt; ( &lt;a href="http://cran.r-project.org/web/packages/stringr/stringr.pdf" rel="nofollow noreferrer"&gt;http://cran.r-project.org/web/packages/stringr/stringr.pdf&lt;/a&gt; )&lt;/p&gt;
+&lt;p&gt;EDIT: Code that appears to work for me&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;library(XML)
+library(RCurl)
+options(RCurlOptions = list(cainfo = system.file("CurlSSL", "cacert.pem", package = "RCurl")))
+library(stringr)
+path&amp;lt;-"https://fr.wikipedia.org/wiki/Jeux_olympiques_d%27hiver_de_2010"
+webpage &amp;lt;- getURL(path)
+webpage &amp;lt;- readLines(tc &amp;lt;- textConnection(webpage)); close(tc)
+pagetree &amp;lt;- htmlTreeParse(webpage, error=function(...){}, useInternalNodes = TRUE, encoding = "UTF-8")
+# Extract table header and contents
+tablehead &amp;lt;- xpathSApply(pagetree, "//*/table/tr", xmlValue)
+country&amp;lt;-tablehead[31]
+country&amp;lt;-strsplit(country,"\n")
+# extract country
+bar &amp;lt;- function(x) str_trim(str_extract(x, "[^(]*"), side = "both")
+res1 &amp;lt;- sapply(country[[1]], bar)    
+# extract nb of athletes
+foo &amp;lt;- function(x) str_trim(str_match(x, "\\((.*?)\\)")[[2]], side = "both")
+res2 &amp;lt;- sapply(country[[
+[K2]
+Q: Charset for foreign languages
+A: &lt;p&gt;I suggest using UTF-8, that can encode any Unicode character.&lt;/p&gt;
+&lt;p&gt;But apart from declaring the encoding in the document itself, it’s more important that your code is actually encoded in UTF-8. So get yourself a editor that can handle this encoding properly and declare the encoding in the HTTP header as it has a &lt;a href="http://www.w3.org/TR/html4/charset.html#spec-char-encoding" rel="nofollow noreferrer"&gt;higher priority&lt;/a&gt;.&lt;/p&gt;
+[K3]
+code&gt;raise&lt;/code&gt; without an exception argument? That syntax is only allowed inside an &lt;code&gt;except&lt;/code&gt; block, and raises the exception currently being handled.  It doesn't work outside an &lt;code&gt;except&lt;/code&gt; block.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://github.com/brack3t/Djrill/issues/1" rel="nofollow"&gt;An open issue&lt;/a&gt; in Djrill mentions a send failure and links a fork that supposedly fixes it.  I suspect Djrill isn't well supported and you might try that fork or another solution entirely.&lt;/p&gt;
+[K4]
+Q: JSON Specification and usage of BOM/charset-encoding
+A: &lt;h2&gt;You are right&lt;/h2&gt;
+&lt;ol&gt;
+&lt;li&gt;&lt;strong&gt;The BOM character is illegal in JSON&lt;/strong&gt; (and not needed)&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;The MIME charset is illegal in JSON&lt;/strong&gt; (and not needed as well)&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;&lt;a href="https://www.rfc-editor.org/rfc/rfc7159#section-8.1" rel="noreferrer"&gt;RFC 7159, Section 8.1&lt;/a&gt;:&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;&lt;strong&gt;Implementations MUST NOT add a byte order mark to the beginning of a JSON text.&lt;/strong&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;This is put as clearly as it can be. This is the only &amp;quot;MUST NOT&amp;quot; in the entire RFC.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.rfc-editor.org/rfc/rfc7159#section-11" rel="noreferrer"&gt;RFC 7159, Section 11&lt;/a&gt;:&lt;/p&gt;
+&lt;blockquote&gt;
+&lt;p&gt;The MIME media type for JSON text is application/json.&lt;br/&gt;
+Type name:  application&lt;br/&gt;
+Subtype name:  json&lt;br/&gt;
+Required parameters:  n/a&lt;br/&gt;
+Optional parameters:  n/a&lt;br/&gt;
+[...]&lt;br/&gt;
+Note:  &lt;strong&gt;No &amp;quot;charset&amp;quot; parameter is defined for this registration.&lt;/strong&gt;&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;h2&gt;JSON encoding&lt;/h2&gt;
+&lt;p&gt;The only valid encodings of JSON are UTF-8, UTF-16 or UTF-32 and since the first character (or first two if there is more than one character) will always have a Unicode value lower than 128 (there is no valid JSON text that can include higher values of the first two characters) it is always possible to know which of the valid encodings and which endianness was used just by looking at the byte stream.&lt;/p&gt;
+&lt;h
+[K5]
+Q: wget: Unsupported scheme on non-http URL
+A: &lt;p&gt;wget for windows doesn't support https&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;unsupported scheme&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;tested : GNU Wget 1.9.1, a non-interactive network retriever&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2190,10 +3568,21 @@
 By following this approach, you will have a clear and reusable way to convert strings into `RenderFragment` while maintaining performance and security in your Blazor applications.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2220,14 +3609,54 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover specific recommendations for a server operating system tailored to your requirements of running a basic server to handle file storage and scheduled synchronization with OneDrive and Google Drive. However, they do mention that if you are technically skilled, you might consider using a lightweight operating system like Linux (Ubuntu) for a server setup, especially if you have the capability to maintain production machines (). 
-The suggestion of using Ubuntu as a server OS is aligned with what you've heard about it being suitable for your needs; however, specific configurations or steps on how to implement the synchronization are not covered in the available context. Therefore, while it's clear Ubuntu is a potential option, further details or guidance on your exact requirement are not available.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] specific recommendations for a server operating system tailored to your requirements of running a basic server to handle file storage and scheduled synchronization with OneDrive and Google Drive. However, they do mention that if you are technically skilled, you might consider using a lightweight operating system like Linux (Ubuntu) for a server setup, especially if you have the capability to maintain production machines (). 
+The suggestion of using Ubuntu as a server OS is aligned with what you've heard about it being suitable for your needs; however, specific configurations or steps on how to implement the synchronization are not covered. Therefore, while it's clear Ubuntu is a potential option, further details or guidance on your exact requirement are not available.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Database on a server without installation?
+A: &lt;p&gt;If you are going to store data on a network share and have concurrent users accessing it you are going to need a db that can handle concurrent access. MS Access will quickly die if under concurrent access as will SQL Lite. &lt;/p&gt;
+&lt;p&gt;SQL Server Express is free and works very well. PostgreSQL as suggested by Maxim is an open source full featured db that will do the job very well but may be overkill.&lt;/p&gt;
+&lt;p&gt;You could also look at Redis ... fast lightweight in memory no sql db that also has capability to persist to file. &lt;/p&gt;
+[K2]
+Q: Developing App with node Express , React and MySQL. How / where should i store images?
+A: &lt;p&gt;It's generally not recommended to store images directly in the db. It's a waste of space, and the performance is usually poor. The most common approach would be to store them in the file system, while you would persist only URLs in the DB. You can also use the Cloud like S3 or as you mentioned Firebase Storage. There's also an option to go with CDN like Cloudflare.&lt;/p&gt;
+&lt;p&gt;If your website is primarily static I would go for CDN or filesystem. Some CDNs offer a pay-as-you-go pricing model, which might be what you want for a low-medium budget website.&lt;/p&gt;
+[K3]
+Q: What is a fast, bulk upload, media management system I can install on my website?
+A: &lt;p&gt;I'd recommend drupal. There are many like it but I'd say that this is one of the best ones.&lt;/p&gt;
+&lt;p&gt;There are thousands of modules you can add and a lot for media.&lt;/p&gt;
+[K4]
+Q: Web server statics repository -or- ZFS vs. NTFS
+A: &lt;p&gt;It all depends on your skill level and how much load you are getting on your servers.&lt;/p&gt;
+&lt;p&gt;If you have spare (physical) resources and have the technical skills and experience to maintain production machines running different operating systems, I'd recommend going running lighttpd on either Linux or FreeBSD. A light OS install with a static file optimized server will perform faster than Apache or IIS on a heavy OS.&lt;/p&gt;
+&lt;p&gt;However, unless you are extremely comfortable with these solutions, just stick to IIS on Windows. Move the static files to their own machine if you have sufficient load. If you aren't currently thinking about multiple ASP.Net frontends, there's probably no need to spin off the static files yet unless we're talking multiple gigabytes of files.&lt;/p&gt;
+[K5]
+Q: Enterprise NoSQL Stack Solution for Mobile/Web
+A: &lt;p&gt;I totally agree with the answer from @Philipp. In the case of using CouchDB you will minimum want to use a proxy server in front to enable SSL.&lt;/p&gt;
+&lt;p&gt;Almost all of your requirements can be fulfilled by CouchDB. Especially the upcoming v2 will give you the "datacenter-needs".&lt;/p&gt;
+&lt;p&gt;But it's simply very complex to answer what should be the right tool for you purpose. If you get some business model requirements on top like lets say: throttling - then you will definitely need an application server middleware like &lt;a href="http://mcavage.me/node-restify/" rel="nofollow"&gt;http://mcavage.me/node-restify/&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;Maybe it's a good idea to spend some money to professionals like
+&lt;a href="http://www.neighbourhood.ie/couchdb-support/" rel="nofollow"&gt;http://www.neighbourhood.ie/couchdb-support/&lt;/a&gt; ? (I'm not involved)&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2269,15 +3698,102 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover detailed steps for installing NumPy specifically on Python 3.3.5 on Mac OSX 10.9. However, one of the sources mentions that if you want to install Python and some commonly used libraries like NumPy and Matplotlib, using Anaconda is highly recommended, as it simplifies the installation process and automatically includes many useful libraries (SO-42096280). 
-If you're determined to install NumPy without using Anaconda, typically using `pip` would be the go-to method, which is not discussed in the provided sources, but is common practice. You can try running the command `pip install numpy` in your terminal after ensuring you have installed Python and pip correctly.
-If issues persist, I would suggest checking whether you need to install Xcode command line tools that help with building packages from source. Again, specific steps to troubleshoot or fix errors related to building or the `setup.py` file were not covered in the retrieved context.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
+          <t>[catatan: informasi tidak tersedia] detailed steps for installing NumPy specifically on Python 3.3.5 on Mac OSX 10.9. However, one of if you want to install Python and some commonly used libraries like NumPy and Matplotlib, using Anaconda is highly recommended, as it simplifies the installation process and automatically includes many useful libraries (SO-42096280). 
+If you're determined to install NumPy without using Anaconda, typically using `pip` would be the go-to method, which is not discussed, but is common practice. You can try running the command `pip install numpy` in your terminal after ensuring you have installed Python and pip correctly.
+If issues persist, I would suggest checking whether you need to install Xcode command line tools that help with building packages from source. Again, specific steps to troubleshoot or fix errors related to building or the `setup.py` file were not covered.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+Q: Why pypy is not recognizing my python 2.7/3.4 modules and packages?
+A: &lt;p&gt;PyPy 2.4 is a rather outdated version which contains no support for numpy (even if you tried to install it separately).&lt;/p&gt;
+&lt;p&gt;In any case it is very unlikely that even a brand-new version of PyPy would reduce the memory usage of a numpy-heavy program.&lt;/p&gt;
+&lt;p&gt;If you're hitting MemoryError at the scale of ~1-3GB of data in a single process, on a 32-bit OS, then it seems clear to me that you need a 64-bit OS.&lt;/p&gt;
+[K2]
+&lt;/strong&gt;: As discussed in the chat: The error was due to the conda env ignoring the CC variable. After installing python+pip via homebrew and the required python packages via pip, this answer's steps worked for the OP.&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;All in all, here's a setup.py that worked for me (macOS 10.5.7, gcc-10):&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;try:
+    from setuptools import setup
+except ImportError:
+    from distutils.core import setup
+from distutils.extension import Extension
+from Cython.Build import cythonize
+from torch.utils.cpp_extension import BuildExtension, CppExtension, CUDAExtension
+import numpy
+# Get the numpy include directory.
+numpy_include_dir = numpy.get_include()
+# Extensions
+# pykdtree (kd tree)
+pykdtree = Extension(
+    'im2mesh.utils.libkdtree.pykdtree.kdtree',
+    sources=[
+        'im2mesh/utils/libkdtree/pykdtree/kdtree.c',
+        'im2mesh/utils/libkdtree/pykdtree/_kdtree_core.c'
+    ],
+    language='c',
+    extra_compile_args=['-std=c99', '-O3', '-fopenmp'],
+    extra_link_args=['-lgomp'],
+    include_dirs=[numpy_include_dir]
+)
+# mcubes (marching cubes algorithm)
+mcubes_module = Extension(
+    'im2mesh.utils.libmcubes.mcubes',
+    sources=[
+        'im2mesh/utils/libmcubes/mcubes.pyx',
+        'im2mesh/utils/libmcubes/pywrapper.cpp',
+        'im2mesh/utils/libmcubes/marchingcubes.cpp'
+    ],
+    language='c++',
+    extra_compile_args=['-std=c++11'],
+    include_dirs=[numpy_include_dir]
+)
+# triangle hash (efficient mesh intersection)
+triangle_hash_module = Extension(
+[K3]
+Q: Google foo.bar Challenge Issue: Can't import libraries
+A: &lt;p&gt;Unfortunately numpy is not a standard library in python 2.7, and is not supported by foobar.  For a complete list of available modules, I suggest looking here: &lt;a href="https://docs.python.org/2/library/" rel="noreferrer"&gt;https://docs.python.org/2/library/&lt;/a&gt;&lt;/p&gt;
+[K4]
+Q: How is Anaconda related to Python?
+A: &lt;p&gt;Anaconda is a Python-based data processing and scientific computing platform. It has built in many very useful third-party libraries. Installing Anaconda is equivalent to automatically installing Python and some commonly used libraries such as Numpy, Pandas, Scrip, and Matplotlib, so it makes the installation so much easier than regular Python installation. If you don't install Anaconda, but instead only install Python from python.org, you also need to use pip to install various libraries one by one. It is painful and you need to consider compatibility, thus it is highly recommended to directly install Anaconda.&lt;/p&gt;
+[K5]
+Q: dpkg error: pycompile: not found
+A: &lt;p&gt;(EDIT: works in Python 3.11 down to 3.5)&lt;/p&gt;
+&lt;p&gt;Ahhhh, yes.  The venerable &amp;quot;Catch-22&amp;quot; situation of Debian package management.  It boils down to Debian depending on &lt;code&gt;py3compile&lt;/code&gt; as part of the &lt;code&gt;libpython3.x&lt;/code&gt; package when that package provides the &lt;code&gt;py3compile&lt;/code&gt; as well; it's a no-go, there.&lt;/p&gt;
+&lt;p&gt;I too was bitten by this unable to get &lt;code&gt;py3compile&lt;/code&gt; working again for I had too deleted the entire /usr/[/local]/lib/python3* directories.&lt;/p&gt;
+&lt;p&gt;Once done, nothing in Debian package management tool can help you get back to a working Python3 environment.  You must do meat-ball surgery.&lt;/p&gt;
+&lt;p&gt;Reconstruction of Python3 in Debian entails three critical things:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Restoring &lt;code&gt;py3compile&lt;/code&gt; script (for most of you, you already have this)&lt;/li&gt;
+&lt;li&gt;Restoring libpython3.7&lt;/li&gt;
+&lt;li&gt;Restoring python binary&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;One could do the RE-copying of /usr[/local]/lib directory from another working Debian host/system. But this time, I shall detail the steps from within the broken host in question (as if you do NOT have another working host).&lt;/p&gt;
+&lt;h1&gt;Step 1 - Download Packages&lt;/h1&gt;
+&lt;p&gt;Download the impacted Debian packages:&lt;/p&gt;
+&lt;pre class="lang-bash prettyprint-override"&gt;&lt;code&gt;cd /tmp
+apt-get download libpython3.7-minimal
+apt-get download python3.7-minimal
+apt-get download python3-minimal # (this is important)
+apt-get download libpython3.7-stdlib</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2313,10 +3829,74 @@
 In summary, instead of using `addChild()`, leverage `addElement()` for adding elements in Flex containers to align with the framework's design principles.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: Migrating to Flex mxmlc from ActionScript 2 mtasc
+A: &lt;p&gt;I don't think I can answer all of your question, but I'll try to provide some answers:&lt;/p&gt;
+&lt;p&gt;ActionScript 3 is a substantial change from ActionScript 2. Its a complete architectural overhaul, not just a minor update and its not backwards compatible, so short of a re-write, its usually pretty difficult to tweak non-trivial as2 to compile as as3. It's pretty much like an entirely new language . So it might be best to take a step back and see whats changed in the language, because it's a lot. &lt;/p&gt;
+&lt;p&gt;The biggest thing is the formalized &lt;a href="http://help.adobe.com/en_US/ActionScript/3.0_ProgrammingAS3/WS5b3ccc516d4fbf351e63e3d118a9b90204-7f36.html" rel="nofollow"&gt;class inheritance&lt;/a&gt;, over prototypical inheritance.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;"Flash will simply create an instance of the "main class"', whatever that is."&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;So, when you compile from the command-line, you give it the path to the "main class":&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;mxmlc.exe "c:\dev\project\SomeClass.as"&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;with &lt;code&gt;SomeClass.as&lt;/code&gt; looking like this:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package {
+    import flash.display.Sprite;
+    public class SomeClass extends Sprite {}
+}
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;Upon initialization, flash will create an instance of this class and attach it to the stage. This will be the similar to the AS2 concept of &lt;code&gt;_root&lt;/code&gt;. The &lt;code&gt;-src&lt;/code&gt; switch passed to &lt;code&gt;mxmlc.exe&lt;/code&gt; sets the path to the rest
+[K2]
+Q: Exact difference between add-ons, plugins and extensions
+A: &lt;p&gt;General rule of thumb:&lt;/p&gt;
+&lt;h2&gt;Plugins&lt;/h2&gt;
+&lt;p&gt;When you're talking about a web browser, a plugin talks about a NPAPI or similar plugin, which is specific to the page. IE doesn't support "plugins" per se, but they have activex controls which can fill a similar function, though there are also BHO (Browser Helper Object) ActiveX controls which are more similar to extensions.  Thus we (the FireBreath team) usually use the term "plugin" to refer to something that works like a NPAPI plugin and the term "extension" to refer to something that works like a typical extension (firefox XPI, Chrome CRX, etc).&lt;/p&gt;
+&lt;p&gt;Plugins only know about the page they are in; they don't know anything else about the browser or what is loaded in other pages.&lt;/p&gt;
+&lt;p&gt;Plugins have been responsible for a lot of security problems, since they actually run native code.  This has led to a lot of discrimination against them -- much of it deserved.  Because of this, and because NPAPI is a royal pain in the neck (hence FireBreath was created), most browsers are trying to phase out plugins.  Plugins should never be used unless there is no other way to solve your problem.&lt;/p&gt;
+&lt;p&gt;That said, there are a lot of cases where they are the only option.&lt;/p&gt;
+&lt;h2&gt;Extensions&lt;/h2&gt;
+&lt;p&gt;An extension is something that is specific to the browser, and they are a bit different on each browser, but tend to be able to learn more about the overall state of the browser; they may be automatically added to pages, accessible separately from a page, etc.&lt;/p&gt;
+&lt;h2&gt;Add-ons&lt;/h2&gt;
+&lt;p&gt;Add-on is more of a generic term which is used to mean a lot of different things.  What it actually means
+[K3]
+Q: Is Flash or Flex better to build a user interactive ordering "wizard" website?
+A: &lt;p&gt;Short answer is &lt;strong&gt;to take best from both of them.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;And here is a short story, which describe how big Flash project could be done.&lt;/p&gt;
+&lt;p&gt;Company receive order for a project X, and there are two departments are going to work on it, D (Designers who are going to create all fancy graphic for the project) and P (Programmers who are going to input some life into the lifeless design). &lt;/p&gt;
+&lt;p&gt;While guys from the P department drinking bear in the basement and creating data model for the project X, configuring software, and doing all routine stuff that are need to be done before starting a new project. Guys from the D department open &lt;strong&gt;Flash&lt;/strong&gt; which is familiar for them, as they spent all their life in Ps,Ai and other Adobe products. (&lt;em&gt;Flash is good, really good, if you want to play with a graphic objects. Move them left or right, add some fancy effects, create animation and stuff like that. Creating graphical objects for the future Flash project inside the Flash IDE is more natural.&lt;/em&gt;). &lt;/p&gt;
+&lt;p&gt;Nobody from the D department had never write a line of code, so when they finish creating first part of graphical assets they just compile this to the .swc file and pass it to the P department, where good fellows already start to wrote some code inside &lt;strong&gt;Flash Builder&lt;/strong&gt; which is  looks familiar for them, as they  spent a lot amount of time coding with different programming languages inside &lt;a href="http://en.wikipedia.org/wiki/List_of_Eclipse-based_software" rel="nofollow"&gt;Eclipse based IDE&lt;/a&gt;. &lt;/p&gt;
+&lt;p&gt;So in the end the project X, is nicely separated into the two parts: graphical assets which are created inside Flash - which was
+[K4]
+ just depends on who is talking, but the mozilla definition is probably as good as any; it could be anything that adds functionality to your web browser, regardless of the context.&lt;/p&gt;
+&lt;h2&gt;Key Differences&lt;/h2&gt;
+&lt;p&gt;Extensions tend to be automatic once installed.  Plugins are instantiated in one of two ways: 1) by an &lt;code&gt;&amp;lt;object&amp;gt;&lt;/code&gt; or &lt;code&gt;&amp;lt;embed&amp;gt;&lt;/code&gt; tag in the HTML of a web page, or 2) because they are registered to be the handler for a mimetype which the browser doesn't support.&lt;/p&gt;
+&lt;h1&gt;FireBreath&lt;/h1&gt;
+&lt;p&gt;FireBreath deals with plugins.  It has nothing to do with typical browser extensions, only plugins.  It is a C++ framework, not a javascript framework, and it allows you to add functionality that can be used from within a web page.  Typically FireBreath plugins are used from inside a &lt;code&gt;&amp;lt;object&amp;gt;&lt;/code&gt; tag.&lt;/p&gt;
+&lt;h1&gt;FireBreath post-NPAPI&lt;/h1&gt;
+&lt;p&gt;As you may or may not know, Chrome has dropped support for NPAPI plugins (as of version 45) and Firefox has done so as of version 52 (excluding the version 52 Extended Support Release, which will support them for another year).  FireBreath 2.0 is now being used in production by several companies and can produce "plugins" (not really plugins, but work similarly) which can work with Google Chrome and Firefox via Native Messaging via a helper extension. The main limitation is drawing; there is no way to draw directly to the browser across native messaging (well, no good way, and no way at all on platforms other than windows).&lt;/p&gt;
+&lt;p&gt;Eventually we may add support for some abstraction to draw using Canvas / WebGL over the native messaging bridge in FireBreath 2.0, but that hasn
+[K5]
+p&gt;
+&lt;p&gt;One key difference is not &lt;code&gt;f&lt;/code&gt; can be restricted to only working on &lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2406,10 +3986,21 @@
 Both methods can be useful depending on your design needs. Understanding the context in which you're using them will help you decide which one to apply. For layouts where the element should always fill the visible space regardless of content, `100vh` is great. For content-driven layouts, `100%` might be better.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2547,10 +4138,21 @@
 While there is no direct integration for reading GRASS layers into GeoPandas, your current approach is quite effective. The improved method further cleans up your logic, making it clearer and easier to maintain while ensuring good practices around resource management.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2647,10 +4249,60 @@
 This design will help maintain clarity and ensure that all contributions can be flexibly assigned based on your stated criteria.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: How do I design a chart of accounts for an accounting system using PHP
+A: &lt;p&gt;You may use a hierarchical data model like a nested set or a closure table. In this approach, each node in the tree is represented as a row in a database table, and the relationship between nodes is encoded using additional columns in the table. This approach allows for efficient querying of the tree structure and is suitable for handling a large number of nodes. Or you may use a recursive data model, where each node in the tree is represented as an object that contains a list of its child nodes. This approach is simpler and more intuitive to work with, but may be less efficient for large trees.
+You may also want to have a look at some APIs like Java Tree API and their documentation to get some more insight about the idea.&lt;/p&gt;
+[K2]
+Q: How to visualize the relationship of tables in an Oracle database
+A: &lt;p&gt;There is no inbuilt tool, but you can use some free ware, or even buy some of these if you really like them.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool"&gt;https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/433071/good-tool-to-visualise-database-schema"&gt;Good tool to visualise database schema?&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;My personal favorite is &lt;a href="http://www.embarcadero.com/products/er-studio" rel="nofollow noreferrer"&gt;ER/Studio&lt;/a&gt;&lt;/p&gt;
+[K3]
+ a table that is at the end child point and its data is not so important.&lt;/p&gt;
+[K4]
+Q: Polymorphism in databases
+A: &lt;p&gt;&lt;strong&gt;The OO structure of your data&lt;/strong&gt; &lt;/p&gt;
+&lt;p&gt;You have identified several classes in your &lt;code&gt;Character&lt;/code&gt; population, that are derived from the abstract role , namely &lt;code&gt;Attack&lt;/code&gt;, &lt;code&gt;Defense&lt;/code&gt; and &lt;code&gt;Support&lt;/code&gt;. Each kind of role has different attributes depending on the class.  &lt;/p&gt;
+&lt;p&gt;So you have clearly an OOP design in your mind and want to implement it in a database.  Several design patterns could be used :   &lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;The easiest seems to be the &lt;a href="http://www.martinfowler.com/eaaCatalog/singleTableInheritance.html" rel="noreferrer"&gt;single table inheritance&lt;/a&gt; puts all the fields in a single table.  These are used/interpreted depending on the concrete role.  &lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://martinfowler.com/eaaCatalog/classTableInheritance.html" rel="noreferrer"&gt;class table inheritance&lt;/a&gt; puts the data related to each role (and the character itself) in a distinct table. This requires a 1:1 relation between the derived class' table (e.g. &lt;code&gt;Defense&lt;/code&gt;) and the parent class table (here &lt;code&gt;Character&lt;/code&gt;).  This seems an overkill here&lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://www.martinfowler.com/eaaCatalog/concreteTableInheritance.html" rel="noreferrer"&gt;concrete table inheritance&lt;/a&gt; merges the parent classes with the most derived classes, so you'd end up with a table per role, each having its own &lt;code&gt;name&lt;/code&gt; field.  Again, this seems an overkill here. &lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Classes or relations ?&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is another additional model that you could consider.
+[K5]
+Q: How to optimize long query that displays thousands of data
+A: &lt;p&gt;Several of your tables need this 'composite' index:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;INDEX(allotment_code, category_name, ntp_number, activity)  -- in any order
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;payroll_transaction&lt;/code&gt; needs &lt;code&gt;INDEX(contractor_name)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;payroll_billed_units&lt;/code&gt; needs &lt;code&gt;INDEX(billing_date)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;For further discussion, please provide &lt;code&gt;SHOW CREATE TABLE&lt;/code&gt; for each table and &lt;code&gt;EXPLAIN SELECT ...&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;Use simply &lt;code&gt;COUNT(*)&lt;/code&gt; instead of &lt;code&gt;COUNT(foo)&lt;/code&gt;.  The latter checks the column for being not-NULL before including it.  This is usually not needed.  The reader is confused by thinking that there might be NULLs.&lt;/p&gt;
+&lt;p&gt;Your &lt;code&gt;GROUP BY&lt;/code&gt; is improper because it is missing &lt;code&gt;ntp_number&lt;/code&gt;.  Read about the &lt;code&gt;sql_mode&lt;/code&gt; of &lt;code&gt;ONLY_FULL_GROUP_BY&lt;/code&gt;.  I bring this up because you can almost get rid of some of those subqueries.&lt;/p&gt;
+&lt;p&gt;Another issue...  Because of the "inflate-deflate" nature of &lt;code&gt;JOIN&lt;/code&gt; with &lt;code&gt;GROUP BY&lt;/code&gt;, the numbers may be inflated.  I recommend you manually check the values of the &lt;code&gt;COUNTs&lt;/code&gt;.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2704,14 +4356,64 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>The retrieved sources do not cover the specifics of how to design your Oracle APEX application to handle family contributions, including how to specifically address the handling of the `CONTRIBUTORS`. It discusses some general database design patterns for creating hierarchical relationships and polymorphism in object-oriented data structures, but does not directly apply to the structure you provided for handling family contributions based on the criteria you laid out.
+          <t>[catatan: informasi tidak tersedia] the specifics of how to design your Oracle APEX application to handle family contributions, including how to specifically address the handling of the `CONTRIBUTORS`. It discusses some general database design patterns for creating hierarchical relationships and polymorphism in object-oriented data structures, but does not directly apply to the structure you provided for handling family contributions based on the criteria you laid out.
 For more specialized advice on this scenario, additional context or resources regarding APEX-specific features, handling many-to-many relationships, or conditionally assigning contributions in Oracle databases would be essential.</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[K1]
+Q: How do I design a chart of accounts for an accounting system using PHP
+A: &lt;p&gt;You may use a hierarchical data model like a nested set or a closure table. In this approach, each node in the tree is represented as a row in a database table, and the relationship between nodes is encoded using additional columns in the table. This approach allows for efficient querying of the tree structure and is suitable for handling a large number of nodes. Or you may use a recursive data model, where each node in the tree is represented as an object that contains a list of its child nodes. This approach is simpler and more intuitive to work with, but may be less efficient for large trees.
+You may also want to have a look at some APIs like Java Tree API and their documentation to get some more insight about the idea.&lt;/p&gt;
+[K2]
+Q: How to visualize the relationship of tables in an Oracle database
+A: &lt;p&gt;There is no inbuilt tool, but you can use some free ware, or even buy some of these if you really like them.&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool"&gt;https://stackoverflow.com/questions/674911/light-weight-er-diagram-tool&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a href="https://stackoverflow.com/questions/433071/good-tool-to-visualise-database-schema"&gt;Good tool to visualise database schema?&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;My personal favorite is &lt;a href="http://www.embarcadero.com/products/er-studio" rel="nofollow noreferrer"&gt;ER/Studio&lt;/a&gt;&lt;/p&gt;
+[K3]
+ a table that is at the end child point and its data is not so important.&lt;/p&gt;
+[K4]
+Q: Polymorphism in databases
+A: &lt;p&gt;&lt;strong&gt;The OO structure of your data&lt;/strong&gt; &lt;/p&gt;
+&lt;p&gt;You have identified several classes in your &lt;code&gt;Character&lt;/code&gt; population, that are derived from the abstract role , namely &lt;code&gt;Attack&lt;/code&gt;, &lt;code&gt;Defense&lt;/code&gt; and &lt;code&gt;Support&lt;/code&gt;. Each kind of role has different attributes depending on the class.  &lt;/p&gt;
+&lt;p&gt;So you have clearly an OOP design in your mind and want to implement it in a database.  Several design patterns could be used :   &lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;The easiest seems to be the &lt;a href="http://www.martinfowler.com/eaaCatalog/singleTableInheritance.html" rel="noreferrer"&gt;single table inheritance&lt;/a&gt; puts all the fields in a single table.  These are used/interpreted depending on the concrete role.  &lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://martinfowler.com/eaaCatalog/classTableInheritance.html" rel="noreferrer"&gt;class table inheritance&lt;/a&gt; puts the data related to each role (and the character itself) in a distinct table. This requires a 1:1 relation between the derived class' table (e.g. &lt;code&gt;Defense&lt;/code&gt;) and the parent class table (here &lt;code&gt;Character&lt;/code&gt;).  This seems an overkill here&lt;/li&gt;
+&lt;li&gt;The &lt;a href="http://www.martinfowler.com/eaaCatalog/concreteTableInheritance.html" rel="noreferrer"&gt;concrete table inheritance&lt;/a&gt; merges the parent classes with the most derived classes, so you'd end up with a table per role, each having its own &lt;code&gt;name&lt;/code&gt; field.  Again, this seems an overkill here. &lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Classes or relations ?&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is another additional model that you could consider.
+[K5]
+Q: How to optimize long query that displays thousands of data
+A: &lt;p&gt;Several of your tables need this 'composite' index:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;INDEX(allotment_code, category_name, ntp_number, activity)  -- in any order
+&lt;/code&gt;&lt;/pre&gt;
+&lt;p&gt;&lt;code&gt;payroll_transaction&lt;/code&gt; needs &lt;code&gt;INDEX(contractor_name)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;&lt;code&gt;payroll_billed_units&lt;/code&gt; needs &lt;code&gt;INDEX(billing_date)&lt;/code&gt;, though it may not get used.&lt;/p&gt;
+&lt;p&gt;For further discussion, please provide &lt;code&gt;SHOW CREATE TABLE&lt;/code&gt; for each table and &lt;code&gt;EXPLAIN SELECT ...&lt;/code&gt;&lt;/p&gt;
+&lt;p&gt;Use simply &lt;code&gt;COUNT(*)&lt;/code&gt; instead of &lt;code&gt;COUNT(foo)&lt;/code&gt;.  The latter checks the column for being not-NULL before including it.  This is usually not needed.  The reader is confused by thinking that there might be NULLs.&lt;/p&gt;
+&lt;p&gt;Your &lt;code&gt;GROUP BY&lt;/code&gt; is improper because it is missing &lt;code&gt;ntp_number&lt;/code&gt;.  Read about the &lt;code&gt;sql_mode&lt;/code&gt; of &lt;code&gt;ONLY_FULL_GROUP_BY&lt;/code&gt;.  I bring this up because you can almost get rid of some of those subqueries.&lt;/p&gt;
+&lt;p&gt;Another issue...  Because of the "inflate-deflate" nature of &lt;code&gt;JOIN&lt;/code&gt; with &lt;code&gt;GROUP BY&lt;/code&gt;, the numbers may be inflated.  I recommend you manually check the values of the &lt;code&gt;COUNTs&lt;/code&gt;.&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2752,10 +4454,123 @@
 By following these steps, you should be able to successfully configure your AWS Lambda function to work with Java 11 and deploy it without errors. Make sure to verify every component of your setup to ensure compatibility with the Java version you are trying to use.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>[K1]
+$registerAndPromoteBean$1(AwsSecretsManagerConfigDataLocationResolver.java:113) ~[spring-cloud-starter-aws-secrets-manager-config-2.3.0-RC2.jar:2.3.0-RC2]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.doInvokeListener(SimpleApplicationEventMulticaster.java:176) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.invokeListener(SimpleApplicationEventMulticaster.java:169) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:143) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.context.event.SimpleApplicationEventMulticaster.multicastEvent(SimpleApplicationEventMulticaster.java:131) ~[spring-context-5.3.3.jar:5.3.3]
+        at org.springframework.boot.DefaultBootstrapContext.close(DefaultBootstrapContext.java:133) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.prepareContext(SpringApplication.java:392) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:325) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1311) ~[spring-boot-2.4.2.jar:2.4.2]
+        at org.springframework.boot.SpringApplication.run(SpringApplication.java:1300) ~[spring-boot-2.4.2.jar:2.4.2]
+        at com.brighttalk.service.securedsecrets
+[K2]
+Q: Tomcat fails to start using Eclipse, JRebel, and Spring Boot
+A: &lt;p&gt;JRebel cannot instrument class because &lt;em&gt;MBeanRegistrationSupport#setRegistrationBehavior&lt;/em&gt; method was removed by &lt;a href="https://github.com/spring-projects/spring-framework/commit/b5db5d3aac39ca7cff4ccca491652d9490a1d175#diff-c36e12d89e096da6108d667fb27b1c3dL165" rel="nofollow"&gt;b5db5d&lt;/a&gt; commit on spring-framework development branch.&lt;/p&gt;
+&lt;p&gt;We have updated our Spring integration and &lt;a href="https://zeroturnaround.com/software/jrebel/download/nightly-build/" rel="nofollow"&gt;JRebel Nighly build&lt;/a&gt; (choose standalone jar) should work fine.&lt;/p&gt;
+&lt;p&gt;Fix will be included in JRebel 6.5.2 which we plan to release next week.&lt;/p&gt;
+&lt;p&gt;Thank you for bug report, if you have any questions/issue please write to support@zeroturnaround.com.&lt;/p&gt;
+[K3]
+Q: SpringMVC XML error- Randomly
+A: &lt;p&gt;This kind of issue:&lt;/p&gt;
+&lt;blockquote&gt;
+  &lt;p&gt;cvc-elt.1: Cannot find the declaration of element 'beans'.
+  root-context.xml /SwiftEmploymentMVC/src/main/webapp/WEB-INF/spring
+  line 3 XML Problem&lt;/p&gt;
+&lt;/blockquote&gt;
+&lt;p&gt;generally is a &lt;strong&gt;dependency one&lt;/strong&gt;, that is caused by some &lt;strong&gt;missing classes&lt;/strong&gt;, themselves caused by using &lt;strong&gt;conflicting dependencies versions&lt;/strong&gt;.
+Even if you say everything is fine with your Apache server, you are using &lt;strong&gt;too much different versions for your Spring jars&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;By example, you use &lt;code&gt;spring-security-core&lt;/code&gt; in version &lt;code&gt;3.1.0.RELEASE&lt;/code&gt;, but &lt;code&gt;spring-security-config&lt;/code&gt; in version &lt;code&gt;4.0.3.RELEASE&lt;/code&gt;.
+Those jars are linked, and you are using 2 different major versions, which could be a problem.&lt;/p&gt;
+&lt;p&gt;If you don't know &lt;strong&gt;which dependencies versions are required by a jar&lt;/strong&gt;, have a look at &lt;a href="http://mvnrepository.com/" rel="nofollow"&gt;http://mvnrepository.com/&lt;/a&gt;.&lt;br&gt;
+It lists the different required dependencies by type.&lt;/p&gt;
+&lt;p&gt;If your case, I would suggest that you use your &lt;code&gt;org.springframework-version&lt;/code&gt; property for more (or all) of your Spring jars.&lt;/p&gt;
+[K4]
+Q: Error Creating Bean Error (Spring Cloud Config Client)
+A: &lt;p&gt;With help for Gregor, I was able to solve it. These are the changes I did:&lt;/p&gt;
+&lt;p&gt;I added a &lt;code&gt;messageConverter&lt;/code&gt;:&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;package com.gcp.logicalprovisioning.config.server;
+import org.slf4j.Logger;
+import org.slf4j.LoggerFactory;
+import org.springframework.beans.factory.annotation.Value;
+import org.springframework.boot.CommandLineRunner;
+import org.springframework.boot.SpringApplication;
+import org.springframework.boot.autoconfigure.EnableAutoConfiguration;
+import org.springframework.boot.autoconfigure.SpringBootApplication;
+import org.springframework.boot.autoconfigure.jdbc.DataSourceAutoConfiguration;
+import org.springframework.context.annotation.Bean;
+@SpringBootApplication
+@EnableAutoConfiguration(exclude={DataSourceAutoConfiguration.class})
+public class DemoClientApplication {
+    private static final Logger LOGGER = LoggerFactory.getLogger(DemoClientApplication.class);
+    public static void main(String[] args) {
+        SpringApplication.run(DemoClientApplication.class, args);
+    }
+    /**
+     * Output property from cloud-config-server on startup of app,
+     *
+     * also can be seen at:
+     * http://localhost:9090/env/APP.aaf.env
+     */
+    @Bean
+    public CommandLineRunner printProperties(@Value(&amp;quot;${APP.aaf.env}&amp;quot;) final String appProperty)  {
+        return args -&amp;gt; LOGGER.info(&amp;quot;APP.aaf.env is: [{}]&amp;quot;, appProperty);
+    }
+    @Bean
+    public RestTemplate restTemplate() {
+        final RestTemplate restTemplate = new RestTemplate();
+        List&amp;lt;HttpMessageConverter&amp;lt;?&amp;gt;&amp;gt; messageConverters = new ArrayList&amp;lt;&amp;gt;();
+        MappingJackson2HttpMessageConverter mappingJackson2HttpMessageConverter = new MappingJackson2HttpMessageConverter();
+        mappingJackson2HttpMessageConverter.setSupportedMediaTypes(Collections.singletonList(MediaType.ALL));
+        messageConverters.add(mappingJackson2HttpMessageConverter);
+        restTemplate.setMessageConverters(messageConverters
+[K5]
+Q: spring batch AsynchJob Launcher ,Error in setting job repo
+A: &lt;p&gt;Here is a working example made from &lt;a href="http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/" rel="nofollow"&gt;http://www.mkyong.com/spring-batch/spring-batch-hello-world-example/&lt;/a&gt; and tested on wildfly 9.&lt;/p&gt;
+&lt;pre&gt;&lt;code&gt;&amp;lt;beans xmlns="http://www.springframework.org/schema/beans"
+       xmlns:batch="http://www.springframework.org/schema/batch" 
+       xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"
+       xsi:schemaLocation="http://www.springframework.org/schema/batch
+        http://www.springframework.org/schema/batch/spring-batch-2.2.xsd
+        http://www.springframework.org/schema/beans 
+        http://www.springframework.org/schema/beans/spring-beans-3.2.xsd
+    "&amp;gt;
+    &amp;lt;bean id="report" class="Report" scope="prototype" /&amp;gt;
+    &amp;lt;bean id="jobRepository"
+       class="org.springframework.batch.core.repository.support.MapJobRepositoryFactoryBean"&amp;gt;
+        &amp;lt;property name="transactionManager" ref="transactionManager" /&amp;gt;
+    &amp;lt;/bean&amp;gt;
+    &amp;lt;batch:job id="helloWorldJob"&amp;gt;
+        &amp;lt;batch:step id="step1"&amp;gt;
+            &amp;lt;batch:tasklet&amp;gt;
+                &amp;lt;batch:chunk reader="cvsItemReader" writer="xmlItemWriter"
+                                     commit-interval="10"&amp;gt;
+                &amp;lt;/batch:chunk&amp;gt;
+            &amp;lt;/batch:tasklet&amp;gt;
+        &amp;lt;/batch:step&amp;gt;
+    &amp;lt;/batch:job&amp;gt;
+    &amp;lt;bean id="jobLauncher"
+              class="org</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2803,21 +4618,44 @@
 By following these guidelines, you should be able to fix the issue and structure your code according to the best practices of the Flex framework.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>annotator2</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="E2:E31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="G2:G31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+    <dataValidation sqref="H2:H31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: PENUH, SEBAGIAN" type="list">
+    <dataValidation sqref="I2:I31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: PENUH, SEBAGIAN" type="list">
       <formula1>"PENUH,SEBAGIAN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: all_supported, partly_supported, not_supported" type="list">
+      <formula1>"all_supported,partly_supported,not_supported"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: same, different_valid, different_unassessable" type="list">
+      <formula1>"same,different_valid,different_unassessable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: familiar, not_familiar" type="list">
+      <formula1>"familiar,not_familiar"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Isi dengan salah satu: Y, N" type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2830,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -2846,35 +4684,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>abstain: Y jika jawaban kandidat tidak mencoba menjawab; N jika mencoba menjawab.</t>
+          <t>Panduan singkat: docs/ANNOTATION_QUICKSTART.md.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hallucinated: isi HANYA jika abstain = N. Y jika ada &gt;= 1 klaim yang bertentangan dengan referensi atau fakta mapan, atau yang dikarang (API/fungsi/opsi tidak ada). N jika tidak ada.</t>
+          <t>annotator_id: sudah terisi; jangan diubah kecuali Anda annotator lain.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>severity: isi HANYA jika hallucinated = Y. PENUH jika kesalahan mengenai solusi utama; SEBAGIAN jika hanya detail sekunder.</t>
+          <t>abstain: Y jika jawaban kandidat tidak mencoba menjawab; N jika mencoba menjawab.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>notes: catatan bebas. Tulis 'referensi usang' bila memakai aturan referensi usang.</t>
+          <t>hallucinated: isi HANYA jika abstain = N. Y jika ada &gt;= 1 klaim yang bertentangan dengan referensi atau fakta mapan, atau yang dikarang (API/fungsi/opsi tidak ada). N jika tidak ada.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jangan mengubah kolom item_id, question, accepted_answer, candidate_answer.</t>
+          <t>severity: isi HANYA jika hallucinated = Y. PENUH jika kesalahan mengenai solusi utama; SEBAGIAN jika hanya detail sekunder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>wrong_claims: WAJIB jika hallucinated = Y, kosong jika tidak. Satu klaim salah per baris (Alt+Enter): jenis | klaim | bukti. jenis = contradicted atau fabricated. bukti = URL dokumentasi, atau kutipan dalam tanda petik dari thread/konteks (mis. "[K2] ... teks ...").</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>faithfulness_level: isi HANYA jika kolom context tidak kosong dan abstain = N: all_supported / partly_supported / not_supported (klaim jawaban didukung konteks?).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>approach_match: isi jika abstain = N: same / different_valid / different_unassessable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>domain_familiarity: selalu isi: familiar / not_familiar (keakraban Anda dengan topiknya).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>uncertain: selalu isi: Y jika Anda ragu pada label baris ini, N jika tidak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>notes: catatan bebas. Tulis 'referensi usang' bila memakai aturan referensi usang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jangan mengubah kolom item_id, question, accepted_answer, candidate_answer, context.</t>
         </is>
       </c>
     </row>
